--- a/research/traditional_assets/database/data/south_korea/south_korea_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ19"/>
+  <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.119</v>
+        <v>0.107</v>
       </c>
       <c r="E2">
-        <v>0.241</v>
+        <v>0.09570000000000001</v>
       </c>
       <c r="G2">
-        <v>0.01958934603135561</v>
+        <v>0.02024453286005512</v>
       </c>
       <c r="H2">
-        <v>0.01869723635636241</v>
+        <v>0.01934550734308201</v>
       </c>
       <c r="I2">
-        <v>0.01323610830273544</v>
+        <v>0.01169286750055079</v>
       </c>
       <c r="J2">
-        <v>0.01087523451531472</v>
+        <v>0.00943300364152635</v>
       </c>
       <c r="K2">
-        <v>2226.581</v>
+        <v>1865.26</v>
       </c>
       <c r="L2">
-        <v>0.08328181008159113</v>
+        <v>0.06929979071779746</v>
       </c>
       <c r="M2">
-        <v>659.5528</v>
+        <v>639.6458</v>
       </c>
       <c r="N2">
-        <v>0.04630276565796263</v>
+        <v>0.05770008208773465</v>
       </c>
       <c r="O2">
-        <v>0.2962177437066067</v>
+        <v>0.3429258119511489</v>
       </c>
       <c r="P2">
-        <v>412.0268</v>
+        <v>364.5058</v>
       </c>
       <c r="Q2">
-        <v>0.02892563016213446</v>
+        <v>0.03288072020711367</v>
       </c>
       <c r="R2">
-        <v>0.1850490954517262</v>
+        <v>0.1954182258773576</v>
       </c>
       <c r="S2">
-        <v>247.526</v>
+        <v>275.14</v>
       </c>
       <c r="T2">
-        <v>0.3752936838415362</v>
+        <v>0.4301443079904534</v>
       </c>
       <c r="U2">
-        <v>7573.947</v>
+        <v>8395.75</v>
       </c>
       <c r="V2">
-        <v>0.5317158733111725</v>
+        <v>0.7573495584401526</v>
       </c>
       <c r="W2">
-        <v>0.1203018572058607</v>
+        <v>0.06105556990119101</v>
       </c>
       <c r="X2">
-        <v>0.02509178839226706</v>
+        <v>0.05435487386065301</v>
       </c>
       <c r="Y2">
-        <v>0.09521006881359367</v>
+        <v>0.006700696040538003</v>
       </c>
       <c r="Z2">
-        <v>0.1966304896403676</v>
+        <v>0.2242416386837519</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.02503324558288245</v>
+        <v>0.0494782563520715</v>
       </c>
       <c r="AC2">
-        <v>-0.02465628384731023</v>
+        <v>-0.04818974293868688</v>
       </c>
       <c r="AD2">
-        <v>107452.608</v>
+        <v>103598.816</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>107452.608</v>
+        <v>103598.816</v>
       </c>
       <c r="AG2">
-        <v>99878.66099999999</v>
+        <v>95203.06600000001</v>
       </c>
       <c r="AH2">
-        <v>0.8829522920367492</v>
+        <v>0.9033374304862568</v>
       </c>
       <c r="AI2">
-        <v>0.8179960051704315</v>
+        <v>0.841733384143411</v>
       </c>
       <c r="AJ2">
-        <v>0.8751842430796012</v>
+        <v>0.8957020537805472</v>
       </c>
       <c r="AK2">
-        <v>0.8068600194054536</v>
+        <v>0.8301468695280303</v>
       </c>
       <c r="AL2">
-        <v>48.076</v>
+        <v>52.452</v>
       </c>
       <c r="AM2">
-        <v>40.294</v>
+        <v>42.124</v>
       </c>
       <c r="AN2">
-        <v>218.2399220082866</v>
+        <v>222.4534925168023</v>
       </c>
       <c r="AO2">
-        <v>7.360720525834097</v>
+        <v>6.000209715549455</v>
       </c>
       <c r="AP2">
-        <v>202.856976602486</v>
+        <v>204.4256425672629</v>
       </c>
       <c r="AQ2">
-        <v>8.782300094306846</v>
+        <v>7.471346500807142</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>COOCON Corporation (KOSDAQ:A294570)</t>
+          <t>Korea Ratings Co., Ltd. (KOSDAQ:A034950)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,113 +721,113 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.0572</v>
+      </c>
+      <c r="E3">
+        <v>0.0706</v>
+      </c>
       <c r="G3">
-        <v>0.3717948717948718</v>
+        <v>0.4712482853223594</v>
       </c>
       <c r="H3">
-        <v>0.2682445759368836</v>
+        <v>0.4705075445816186</v>
       </c>
       <c r="I3">
-        <v>0.2347140039447732</v>
+        <v>0.3278463648834019</v>
       </c>
       <c r="J3">
-        <v>0.1994649401819109</v>
+        <v>0.2347379972565157</v>
       </c>
       <c r="K3">
-        <v>7.03</v>
+        <v>14.7</v>
       </c>
       <c r="L3">
-        <v>0.1386587771203156</v>
+        <v>0.2016460905349794</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>10.5702</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0434094455852156</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.7190612244897959</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>10.5702</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.0434094455852156</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.7190612244897959</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>66.2</v>
+        <v>75.3</v>
       </c>
       <c r="V3">
-        <v>0.1078175895765472</v>
+        <v>0.3092402464065708</v>
       </c>
       <c r="W3">
-        <v>0.1502136752136752</v>
+        <v>0.1719298245614035</v>
       </c>
       <c r="X3">
-        <v>0.02391150380753108</v>
+        <v>0.04949469702255381</v>
       </c>
       <c r="Y3">
-        <v>0.1263021714061442</v>
-      </c>
-      <c r="Z3">
-        <v>6.610169491525428</v>
-      </c>
-      <c r="AA3">
-        <v>1.318497062219412</v>
+        <v>0.1224351275388497</v>
       </c>
       <c r="AB3">
-        <v>0.02391567140159852</v>
-      </c>
-      <c r="AC3">
-        <v>1.294581390817814</v>
+        <v>0.0494768811987231</v>
       </c>
       <c r="AD3">
-        <v>1.02</v>
+        <v>0.458</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.02</v>
+        <v>0.458</v>
       </c>
       <c r="AG3">
-        <v>-65.18000000000001</v>
+        <v>-74.842</v>
       </c>
       <c r="AH3">
-        <v>0.0016584826509707</v>
+        <v>0.001877372334582182</v>
       </c>
       <c r="AI3">
-        <v>0.009121802897513862</v>
+        <v>0.005608758480491807</v>
       </c>
       <c r="AJ3">
-        <v>-0.1187638934441165</v>
+        <v>-0.4437500741144801</v>
       </c>
       <c r="AK3">
-        <v>-1.428759316089435</v>
+        <v>-11.77131173324944</v>
       </c>
       <c r="AL3">
-        <v>0.083</v>
+        <v>0.019</v>
       </c>
       <c r="AM3">
-        <v>-0.178</v>
+        <v>-0.465</v>
       </c>
       <c r="AN3">
-        <v>0.06623376623376623</v>
+        <v>0.01635714285714286</v>
       </c>
       <c r="AO3">
-        <v>143.3734939759036</v>
+        <v>1257.894736842105</v>
       </c>
       <c r="AP3">
-        <v>-4.232467532467533</v>
+        <v>-2.672928571428571</v>
       </c>
       <c r="AQ3">
-        <v>-66.85393258426967</v>
+        <v>-51.39784946236559</v>
       </c>
     </row>
     <row r="4">
@@ -838,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FnGuide Inc. (KOSDAQ:A064850)</t>
+          <t>COOCON Corporation (KOSDAQ:A294570)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -847,112 +847,115 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.2712041884816754</v>
+        <v>0.4845474613686535</v>
       </c>
       <c r="H4">
-        <v>0.2712041884816754</v>
+        <v>0.3929359823399559</v>
       </c>
       <c r="I4">
-        <v>0.2230366492146597</v>
+        <v>0.304635761589404</v>
       </c>
       <c r="J4">
-        <v>0.2078884262816503</v>
+        <v>0.2648201453330382</v>
       </c>
       <c r="K4">
-        <v>5.46</v>
+        <v>0.76</v>
       </c>
       <c r="L4">
-        <v>0.2858638743455497</v>
+        <v>0.01677704194260486</v>
       </c>
       <c r="M4">
-        <v>0.226</v>
+        <v>0.714</v>
       </c>
       <c r="N4">
-        <v>0.002173076923076923</v>
+        <v>0.002692307692307692</v>
       </c>
       <c r="O4">
-        <v>0.04139194139194139</v>
+        <v>0.9394736842105262</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>0.714</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.002692307692307692</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.9394736842105262</v>
       </c>
       <c r="S4">
-        <v>0.226</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>12.3</v>
+        <v>54.6</v>
       </c>
       <c r="V4">
-        <v>0.1182692307692308</v>
+        <v>0.2058823529411765</v>
       </c>
       <c r="W4">
-        <v>0.6197502837684449</v>
+        <v>0.006877828054298643</v>
       </c>
       <c r="X4">
-        <v>0.02426038792774789</v>
+        <v>0.04949902156035903</v>
       </c>
       <c r="Y4">
-        <v>0.595489895840697</v>
+        <v>-0.04262119350606038</v>
       </c>
       <c r="Z4">
-        <v>2.602179836512262</v>
+        <v>1.039229181004818</v>
       </c>
       <c r="AA4">
-        <v>0.5409630711143762</v>
+        <v>0.27520882274803</v>
       </c>
       <c r="AB4">
-        <v>0.02425413060887988</v>
+        <v>0.04949004007505549</v>
       </c>
       <c r="AC4">
-        <v>0.5167089405054963</v>
+        <v>0.2257187826729745</v>
       </c>
       <c r="AD4">
-        <v>5.67</v>
+        <v>0.642</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>5.67</v>
+        <v>0.642</v>
       </c>
       <c r="AG4">
-        <v>-6.630000000000001</v>
+        <v>-53.958</v>
       </c>
       <c r="AH4">
-        <v>0.05170055621409683</v>
+        <v>0.002414968289435078</v>
       </c>
       <c r="AI4">
-        <v>0.1146149181322013</v>
+        <v>0.007082809293704906</v>
       </c>
       <c r="AJ4">
-        <v>-0.06809078771695595</v>
+        <v>-0.2554321583775954</v>
       </c>
       <c r="AK4">
-        <v>-0.1783696529459242</v>
+        <v>-1.49708673214583</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="AM4">
-        <v>-0.183</v>
+        <v>-0.322</v>
       </c>
       <c r="AN4">
-        <v>1.057835820895522</v>
+        <v>0.03732558139534884</v>
+      </c>
+      <c r="AO4">
+        <v>530.7692307692308</v>
       </c>
       <c r="AP4">
-        <v>-1.236940298507463</v>
+        <v>-3.137093023255814</v>
       </c>
       <c r="AQ4">
-        <v>-23.27868852459016</v>
+        <v>-42.85714285714287</v>
       </c>
     </row>
     <row r="5">
@@ -972,46 +975,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.07690000000000001</v>
+        <v>0.0139</v>
       </c>
       <c r="E5">
-        <v>0.46</v>
+        <v>1.173</v>
       </c>
       <c r="G5">
-        <v>0.234338747099768</v>
+        <v>0.3475409836065574</v>
       </c>
       <c r="H5">
-        <v>0.234338747099768</v>
+        <v>0.3475409836065574</v>
       </c>
       <c r="I5">
-        <v>0.1874709976798144</v>
+        <v>0.1524590163934426</v>
       </c>
       <c r="J5">
-        <v>0.155766343660434</v>
+        <v>0.1223204000253181</v>
       </c>
       <c r="K5">
-        <v>5.6</v>
+        <v>2.12</v>
       </c>
       <c r="L5">
-        <v>0.1299303944315545</v>
+        <v>0.06950819672131148</v>
       </c>
       <c r="M5">
-        <v>1.038</v>
+        <v>0.9688000000000001</v>
       </c>
       <c r="N5">
-        <v>0.01071207430340557</v>
+        <v>0.008945521698984304</v>
       </c>
       <c r="O5">
-        <v>0.1853571428571429</v>
+        <v>0.4569811320754718</v>
       </c>
       <c r="P5">
-        <v>1.038</v>
+        <v>0.9688000000000001</v>
       </c>
       <c r="Q5">
-        <v>0.01071207430340557</v>
+        <v>0.008945521698984304</v>
       </c>
       <c r="R5">
-        <v>0.1853571428571429</v>
+        <v>0.4569811320754718</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1020,73 +1023,67 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>5.46</v>
+        <v>7.48</v>
       </c>
       <c r="V5">
-        <v>0.05634674922600619</v>
+        <v>0.06906740535549401</v>
       </c>
       <c r="W5">
-        <v>0.253393665158371</v>
+        <v>0.08249027237354087</v>
       </c>
       <c r="X5">
-        <v>0.02393745763629496</v>
+        <v>0.04951409624421162</v>
       </c>
       <c r="Y5">
-        <v>0.2294562075220761</v>
+        <v>0.03297617612932925</v>
       </c>
       <c r="Z5">
-        <v>3.121604982979648</v>
+        <v>1.467616206332403</v>
       </c>
       <c r="AA5">
-        <v>0.4862409945509311</v>
+        <v>0.1795194014422193</v>
       </c>
       <c r="AB5">
-        <v>0.02393858066283596</v>
+        <v>0.04951030810348728</v>
       </c>
       <c r="AC5">
-        <v>0.4623024138880952</v>
+        <v>0.130009093338732</v>
       </c>
       <c r="AD5">
-        <v>0.542</v>
+        <v>0.466</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.542</v>
+        <v>0.466</v>
       </c>
       <c r="AG5">
-        <v>-4.918</v>
+        <v>-7.014</v>
       </c>
       <c r="AH5">
-        <v>0.005562283204367726</v>
+        <v>0.004284427118768733</v>
       </c>
       <c r="AI5">
-        <v>0.01975074703009985</v>
+        <v>0.02046912061846613</v>
       </c>
       <c r="AJ5">
-        <v>-0.05346698267052249</v>
+        <v>-0.0692494520466797</v>
       </c>
       <c r="AK5">
-        <v>-0.2237285051405696</v>
+        <v>-0.4588512364254874</v>
       </c>
       <c r="AL5">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>-0.157</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>0.05313725490196079</v>
-      </c>
-      <c r="AO5">
-        <v>577.1428571428571</v>
+        <v>0.0762684124386252</v>
       </c>
       <c r="AP5">
-        <v>-0.4821568627450981</v>
-      </c>
-      <c r="AQ5">
-        <v>-51.46496815286624</v>
+        <v>-1.147954173486088</v>
       </c>
     </row>
     <row r="6">
@@ -1106,46 +1103,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>-8.000000000000001e-05</v>
+        <v>0.0728</v>
       </c>
       <c r="E6">
-        <v>-0.00131</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="G6">
-        <v>0.2327746741154562</v>
+        <v>0.1903052064631957</v>
       </c>
       <c r="H6">
-        <v>0.2327746741154562</v>
+        <v>0.1903052064631957</v>
       </c>
       <c r="I6">
-        <v>0.2216014897579144</v>
+        <v>0.1600089766606822</v>
       </c>
       <c r="J6">
-        <v>0.1600455203807159</v>
+        <v>0.1211496537573737</v>
       </c>
       <c r="K6">
-        <v>34</v>
+        <v>31.8</v>
       </c>
       <c r="L6">
-        <v>0.09044958765629157</v>
+        <v>0.07136445242369838</v>
       </c>
       <c r="M6">
-        <v>17.3312</v>
+        <v>14.2592</v>
       </c>
       <c r="N6">
-        <v>0.09150580781414996</v>
+        <v>0.09557104557640753</v>
       </c>
       <c r="O6">
-        <v>0.5097411764705884</v>
+        <v>0.4484025157232705</v>
       </c>
       <c r="P6">
-        <v>17.3312</v>
+        <v>14.2592</v>
       </c>
       <c r="Q6">
-        <v>0.09150580781414996</v>
+        <v>0.09557104557640753</v>
       </c>
       <c r="R6">
-        <v>0.5097411764705884</v>
+        <v>0.4484025157232705</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1154,73 +1151,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>18</v>
+        <v>23.5</v>
       </c>
       <c r="V6">
-        <v>0.09503695881731784</v>
+        <v>0.1575067024128687</v>
       </c>
       <c r="W6">
-        <v>0.09918319719953325</v>
+        <v>0.09054669703872438</v>
       </c>
       <c r="X6">
-        <v>0.02661527755758504</v>
+        <v>0.05302280683731187</v>
       </c>
       <c r="Y6">
-        <v>0.07256791964194821</v>
+        <v>0.03752389020141251</v>
       </c>
       <c r="Z6">
-        <v>1.037537951973503</v>
+        <v>1.08392118705911</v>
       </c>
       <c r="AA6">
-        <v>0.1660533014383415</v>
+        <v>0.1313166765124926</v>
       </c>
       <c r="AB6">
-        <v>0.02488437424603878</v>
+        <v>0.04903033568235376</v>
       </c>
       <c r="AC6">
-        <v>0.1411689271923027</v>
+        <v>0.08228634083013883</v>
       </c>
       <c r="AD6">
-        <v>77.90000000000001</v>
+        <v>66</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>77.90000000000001</v>
+        <v>66</v>
       </c>
       <c r="AG6">
-        <v>59.90000000000001</v>
+        <v>42.5</v>
       </c>
       <c r="AH6">
-        <v>0.2914328469884025</v>
+        <v>0.3066914498141264</v>
       </c>
       <c r="AI6">
-        <v>0.1800739713361073</v>
+        <v>0.1763291477424526</v>
       </c>
       <c r="AJ6">
-        <v>0.2402727637384677</v>
+        <v>0.2217005738132499</v>
       </c>
       <c r="AK6">
-        <v>0.1444766039556199</v>
+        <v>0.12115165336374</v>
       </c>
       <c r="AL6">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="AM6">
-        <v>30.123</v>
+        <v>30.037</v>
       </c>
       <c r="AN6">
-        <v>0.9016203703703703</v>
+        <v>0.8906882591093118</v>
       </c>
       <c r="AO6">
-        <v>2.749174917491749</v>
+        <v>2.360927152317881</v>
       </c>
       <c r="AP6">
-        <v>0.6932870370370371</v>
+        <v>0.5735492577597842</v>
       </c>
       <c r="AQ6">
-        <v>2.765328818510772</v>
+        <v>2.373739055165296</v>
       </c>
     </row>
     <row r="7">
@@ -1231,7 +1228,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sangsangin Co., Ltd. (KOSDAQ:A038540)</t>
+          <t>NICE Holdings Co., Ltd. (KOSE:A034310)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1239,113 +1236,122 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D7">
+        <v>0.145</v>
+      </c>
+      <c r="E7">
+        <v>-0.011</v>
+      </c>
       <c r="G7">
-        <v>0.2166258225550261</v>
+        <v>0.1416881111682965</v>
       </c>
       <c r="H7">
-        <v>0.2146584978443385</v>
+        <v>0.131497683993824</v>
       </c>
       <c r="I7">
-        <v>0.2359882005899705</v>
+        <v>0.0626865671641791</v>
       </c>
       <c r="J7">
-        <v>0.1768792015807179</v>
+        <v>0.04110804506578445</v>
       </c>
       <c r="K7">
-        <v>76.90000000000001</v>
+        <v>32.7</v>
       </c>
       <c r="L7">
-        <v>0.1744951213977763</v>
+        <v>0.01682964487905301</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>57.6177</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.1581166300768387</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>1.762009174311926</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>9.3177</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.02556997804610319</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.2849449541284403</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>48.3</v>
+      </c>
+      <c r="T7">
+        <v>0.8382840689579765</v>
       </c>
       <c r="U7">
-        <v>102.9</v>
+        <v>393.1</v>
       </c>
       <c r="V7">
-        <v>0.2697247706422018</v>
+        <v>1.078759604829857</v>
       </c>
       <c r="W7">
-        <v>0.1585240156668728</v>
+        <v>0.05178967374089326</v>
       </c>
       <c r="X7">
-        <v>0.02842134007800319</v>
+        <v>0.06523970791057779</v>
       </c>
       <c r="Y7">
-        <v>0.1301026755888696</v>
+        <v>-0.01345003416968453</v>
       </c>
       <c r="Z7">
-        <v>0.8964605370219692</v>
+        <v>2.613666935700834</v>
       </c>
       <c r="AA7">
-        <v>0.1585652240370675</v>
+        <v>0.1074427381797407</v>
       </c>
       <c r="AB7">
-        <v>0.0252728338201286</v>
+        <v>0.04850830888454981</v>
       </c>
       <c r="AC7">
-        <v>0.1332923902169389</v>
+        <v>0.05893442929519085</v>
       </c>
       <c r="AD7">
-        <v>261.3</v>
+        <v>717</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>261.3</v>
+        <v>717</v>
       </c>
       <c r="AG7">
-        <v>158.4</v>
+        <v>323.9</v>
       </c>
       <c r="AH7">
-        <v>0.4065028002489111</v>
+        <v>0.6630294063251341</v>
       </c>
       <c r="AI7">
-        <v>0.2854178044784271</v>
+        <v>0.4366094263792473</v>
       </c>
       <c r="AJ7">
-        <v>0.293387664382293</v>
+        <v>0.47057968908906</v>
       </c>
       <c r="AK7">
-        <v>0.1949298547871031</v>
+        <v>0.2593067008245937</v>
       </c>
       <c r="AL7">
-        <v>1.23</v>
+        <v>19.9</v>
       </c>
       <c r="AM7">
-        <v>1.075</v>
+        <v>12.43</v>
       </c>
       <c r="AN7">
-        <v>2.347708894878706</v>
+        <v>2.819504522217853</v>
       </c>
       <c r="AO7">
-        <v>84.55284552845528</v>
+        <v>6.120603015075377</v>
       </c>
       <c r="AP7">
-        <v>1.423180592991914</v>
+        <v>1.273692489186001</v>
       </c>
       <c r="AQ7">
-        <v>96.74418604651163</v>
+        <v>9.798873692679003</v>
       </c>
     </row>
     <row r="8">
@@ -1356,7 +1362,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NICE Holdings Co., Ltd. (KOSE:A034310)</t>
+          <t>Sangsangin Co., Ltd. (KOSDAQ:A038540)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1365,121 +1371,121 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.119</v>
+        <v>0.107</v>
       </c>
       <c r="E8">
-        <v>0.00328</v>
+        <v>0.0024</v>
       </c>
       <c r="G8">
-        <v>0.1430588235294118</v>
+        <v>0.2432308644522385</v>
       </c>
       <c r="H8">
-        <v>0.1338039215686274</v>
+        <v>0.2428306168764184</v>
       </c>
       <c r="I8">
-        <v>0.05850980392156863</v>
+        <v>0.1638126676294615</v>
       </c>
       <c r="J8">
-        <v>0.03559390610278563</v>
+        <v>0.1207464380561142</v>
       </c>
       <c r="K8">
-        <v>40.9</v>
+        <v>63</v>
       </c>
       <c r="L8">
-        <v>0.02138562091503268</v>
+        <v>0.1299773055498246</v>
       </c>
       <c r="M8">
-        <v>19.05</v>
+        <v>7.603300000000001</v>
       </c>
       <c r="N8">
-        <v>0.03784266984505364</v>
+        <v>0.02865925367508481</v>
       </c>
       <c r="O8">
-        <v>0.4657701711491443</v>
+        <v>0.1206873015873016</v>
       </c>
       <c r="P8">
-        <v>8.550000000000001</v>
+        <v>7.603300000000001</v>
       </c>
       <c r="Q8">
-        <v>0.01698450536352801</v>
+        <v>0.02865925367508481</v>
       </c>
       <c r="R8">
-        <v>0.2090464547677262</v>
+        <v>0.1206873015873016</v>
       </c>
       <c r="S8">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>0.5511811023622047</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>539.8</v>
+        <v>185.2</v>
       </c>
       <c r="V8">
-        <v>1.072308303535956</v>
+        <v>0.6980776479457218</v>
       </c>
       <c r="W8">
-        <v>0.06748061376010558</v>
+        <v>0.1108374384236453</v>
       </c>
       <c r="X8">
-        <v>0.03244671193811031</v>
+        <v>0.05568694088399413</v>
       </c>
       <c r="Y8">
-        <v>0.03503390182199527</v>
+        <v>0.05515049753965119</v>
       </c>
       <c r="Z8">
-        <v>2.839222090261282</v>
+        <v>0.7049156486329261</v>
       </c>
       <c r="AA8">
-        <v>0.1010590044857148</v>
+        <v>0.08511605370244114</v>
       </c>
       <c r="AB8">
-        <v>0.02580530250419652</v>
+        <v>0.04884000694358601</v>
       </c>
       <c r="AC8">
-        <v>0.07525370198151832</v>
+        <v>0.03627604675885513</v>
       </c>
       <c r="AD8">
-        <v>651.8</v>
+        <v>205.6</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>651.8</v>
+        <v>205.6</v>
       </c>
       <c r="AG8">
-        <v>112</v>
+        <v>20.40000000000001</v>
       </c>
       <c r="AH8">
-        <v>0.5642313019390582</v>
+        <v>0.436610745381185</v>
       </c>
       <c r="AI8">
-        <v>0.3699835386274621</v>
+        <v>0.2498177399756986</v>
       </c>
       <c r="AJ8">
-        <v>0.1819954501137472</v>
+        <v>0.07140357017850893</v>
       </c>
       <c r="AK8">
-        <v>0.09166052868483508</v>
+        <v>0.03198494825964254</v>
       </c>
       <c r="AL8">
-        <v>16.4</v>
+        <v>2.22</v>
       </c>
       <c r="AM8">
-        <v>11.87</v>
+        <v>1.913</v>
       </c>
       <c r="AN8">
-        <v>2.836379460400348</v>
+        <v>2.390697674418604</v>
       </c>
       <c r="AO8">
-        <v>6.823170731707318</v>
+        <v>35.76576576576576</v>
       </c>
       <c r="AP8">
-        <v>0.4873803307223672</v>
+        <v>0.2372093023255815</v>
       </c>
       <c r="AQ8">
-        <v>9.427127211457458</v>
+        <v>41.5054887611082</v>
       </c>
     </row>
     <row r="9">
@@ -1490,7 +1496,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KB No.18 Special Purpose Acquisition Company (KOSDAQ:A323940)</t>
+          <t>Han Kook Capital.Co., Ltd (KOSDAQ:A023760)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1498,23 +1504,29 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D9">
+        <v>0.264</v>
+      </c>
+      <c r="E9">
+        <v>0.7020000000000001</v>
+      </c>
       <c r="G9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>-0.018</v>
+        <v>53.4</v>
       </c>
       <c r="L9">
-        <v>0.4736842105263158</v>
+        <v>0.4881170018281535</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1523,7 +1535,7 @@
         <v>-0</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1532,70 +1544,67 @@
         <v>-0</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0.065</v>
+        <v>360.3</v>
       </c>
       <c r="V9">
-        <v>0.004850746268656716</v>
+        <v>1.953904555314534</v>
       </c>
       <c r="W9">
-        <v>-0.001363636363636364</v>
+        <v>0.1632029339853301</v>
       </c>
       <c r="X9">
-        <v>0.02475760638092423</v>
+        <v>0.1435895404790209</v>
       </c>
       <c r="Y9">
-        <v>-0.0261212427445606</v>
+        <v>0.01961339350630911</v>
       </c>
       <c r="Z9">
-        <v>-0.002553077129803816</v>
+        <v>0.04603214676428512</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.02428851711506063</v>
+        <v>0.04812955984106757</v>
       </c>
       <c r="AC9">
-        <v>-0.02428851711506063</v>
+        <v>-0.04812955984106757</v>
       </c>
       <c r="AD9">
-        <v>1.74</v>
+        <v>2166.6</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.74</v>
+        <v>2166.6</v>
       </c>
       <c r="AG9">
-        <v>1.675</v>
+        <v>1806.3</v>
       </c>
       <c r="AH9">
-        <v>0.1149273447820343</v>
+        <v>0.9215652913653763</v>
       </c>
       <c r="AI9">
-        <v>0.1188524590163934</v>
+        <v>0.8735233641091804</v>
       </c>
       <c r="AJ9">
-        <v>0.1111111111111111</v>
+        <v>0.9073692670919776</v>
       </c>
       <c r="AK9">
-        <v>0.1149228130360206</v>
+        <v>0.8520283018867925</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-0.08599999999999999</v>
-      </c>
-      <c r="AQ9">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1606,7 +1615,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CAPE-ES No.4 Special Purpose Acquisition Company (KOSDAQ:A347140)</t>
+          <t>Samsung Card Co., Ltd. (KOSE:A029780)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1614,104 +1623,110 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D10">
+        <v>-0.486</v>
+      </c>
+      <c r="E10">
+        <v>0.09570000000000001</v>
+      </c>
       <c r="G10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>0.003</v>
+        <v>408</v>
       </c>
       <c r="L10">
-        <v>-0.2307692307692308</v>
+        <v>82.09255533199196</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>170.72</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.06844405243956221</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>0.4184313725490197</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>170.72</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.06844405243956221</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>0.4184313725490197</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>0.6820000000000001</v>
+        <v>924.1</v>
       </c>
       <c r="V10">
-        <v>0.1274766355140187</v>
+        <v>0.3704847051276911</v>
       </c>
       <c r="W10">
-        <v>0.0006423982869379015</v>
+        <v>0.06516843164502373</v>
       </c>
       <c r="X10">
-        <v>0.02435084691843366</v>
+        <v>0.09134451059954737</v>
       </c>
       <c r="Y10">
-        <v>-0.02370844863149576</v>
+        <v>-0.02617607895452365</v>
       </c>
       <c r="Z10">
-        <v>-0.003015541637671074</v>
+        <v>0.0002602802857322412</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.0244832785417054</v>
+        <v>0.04824992603630619</v>
       </c>
       <c r="AC10">
-        <v>-0.0244832785417054</v>
+        <v>-0.04824992603630619</v>
       </c>
       <c r="AD10">
-        <v>0.365</v>
+        <v>13037.1</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0.365</v>
+        <v>13037.1</v>
       </c>
       <c r="AG10">
-        <v>-0.3170000000000001</v>
+        <v>12113</v>
       </c>
       <c r="AH10">
-        <v>0.06386701662292213</v>
+        <v>0.8394027582832198</v>
       </c>
       <c r="AI10">
-        <v>0.07336683417085427</v>
+        <v>0.7057801309015315</v>
       </c>
       <c r="AJ10">
-        <v>-0.06298430359626467</v>
+        <v>0.8292429127901803</v>
       </c>
       <c r="AK10">
-        <v>-0.07384113673421851</v>
+        <v>0.6902859617729858</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-0.04</v>
-      </c>
-      <c r="AQ10">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1731,7 +1746,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.287</v>
+        <v>-0.204</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1746,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>-0.313</v>
+        <v>-1.46</v>
       </c>
       <c r="L11">
-        <v>-0.1121863799283154</v>
+        <v>-0.7525773195876289</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1773,55 +1788,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>19.8</v>
+        <v>10.2</v>
       </c>
       <c r="V11">
-        <v>0.2907488986784141</v>
+        <v>0.2524752475247525</v>
       </c>
       <c r="W11">
-        <v>-0.01121863799283154</v>
+        <v>-0.03067226890756302</v>
       </c>
       <c r="X11">
-        <v>0.02472050107740425</v>
+        <v>0.05085952448706077</v>
       </c>
       <c r="Y11">
-        <v>-0.03593913907023578</v>
+        <v>-0.0815317933946238</v>
       </c>
       <c r="Z11">
-        <v>0.09324866310160429</v>
+        <v>0.05350248207391064</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.02465628384731023</v>
+        <v>0.05011303020224182</v>
       </c>
       <c r="AC11">
-        <v>-0.02465628384731023</v>
+        <v>-0.05011303020224182</v>
       </c>
       <c r="AD11">
-        <v>8.460000000000001</v>
+        <v>6.96</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>8.460000000000001</v>
+        <v>6.96</v>
       </c>
       <c r="AG11">
-        <v>-11.34</v>
+        <v>-3.239999999999999</v>
       </c>
       <c r="AH11">
-        <v>0.1105015673981191</v>
+        <v>0.1469594594594595</v>
       </c>
       <c r="AI11">
-        <v>0.1509097395647521</v>
+        <v>0.1517662450937636</v>
       </c>
       <c r="AJ11">
-        <v>-0.1997885835095138</v>
+        <v>-0.08719052744886974</v>
       </c>
       <c r="AK11">
-        <v>-0.3127413127413127</v>
+        <v>-0.09085810431856421</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1838,7 +1853,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sk No.5 Special Purpose Acquisition Company (KOSDAQ:A337450)</t>
+          <t>NH Special Purpose Acquisition 20 Company (KOSDAQ:A391060)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1846,23 +1861,8 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="G12">
-        <v>-0</v>
-      </c>
-      <c r="H12">
-        <v>-0</v>
-      </c>
-      <c r="I12">
-        <v>-0</v>
-      </c>
-      <c r="J12">
-        <v>-0</v>
-      </c>
       <c r="K12">
-        <v>-0.013</v>
-      </c>
-      <c r="L12">
-        <v>0.3513513513513514</v>
+        <v>0.303</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1871,7 +1871,7 @@
         <v>-0</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1880,70 +1880,73 @@
         <v>-0</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>1.51</v>
+        <v>0.45</v>
       </c>
       <c r="V12">
-        <v>0.2018716577540107</v>
+        <v>0.01139240506329114</v>
       </c>
       <c r="W12">
-        <v>-0.00182328190743338</v>
+        <v>0.007890625</v>
       </c>
       <c r="X12">
-        <v>0.02509178839226706</v>
+        <v>0.05006565938612868</v>
       </c>
       <c r="Y12">
-        <v>-0.02691507029970044</v>
+        <v>-0.04217503438612868</v>
       </c>
       <c r="Z12">
-        <v>-0.005339105339105339</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>-0.001085688405277807</v>
       </c>
       <c r="AB12">
-        <v>0.02529552849689663</v>
+        <v>0.04937975458596065</v>
       </c>
       <c r="AC12">
-        <v>-0.02529552849689663</v>
+        <v>-0.05046544299123846</v>
       </c>
       <c r="AD12">
-        <v>1.35</v>
+        <v>2.89</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>1.35</v>
+        <v>2.89</v>
       </c>
       <c r="AG12">
-        <v>-0.1599999999999999</v>
+        <v>2.44</v>
       </c>
       <c r="AH12">
-        <v>0.1528878822197056</v>
+        <v>0.06817645671148856</v>
       </c>
       <c r="AI12">
-        <v>0.1614832535885168</v>
+        <v>0.08306984765737281</v>
       </c>
       <c r="AJ12">
-        <v>-0.02185792349726775</v>
+        <v>0.05817835002384359</v>
       </c>
       <c r="AK12">
-        <v>-0.02335766423357663</v>
+        <v>0.07105416423995341</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AM12">
-        <v>-0.039</v>
+        <v>-0.429</v>
+      </c>
+      <c r="AO12">
+        <v>-0.632183908045977</v>
       </c>
       <c r="AQ12">
-        <v>-0</v>
+        <v>0.1282051282051282</v>
       </c>
     </row>
     <row r="13">
@@ -1954,7 +1957,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Samsung Card Co., Ltd. (KOSE:A029780)</t>
+          <t>CNH Co., Ltd. (KOSDAQ:A023460)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1962,107 +1965,110 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="E13">
-        <v>0.0548</v>
+      <c r="D13">
+        <v>0.483</v>
       </c>
       <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>-3.01</v>
+      </c>
+      <c r="L13">
+        <v>-0.01646608315098468</v>
+      </c>
+      <c r="M13">
+        <v>2.0076</v>
+      </c>
+      <c r="N13">
+        <v>0.02712972972972973</v>
+      </c>
+      <c r="O13">
+        <v>-0.6669767441860466</v>
+      </c>
+      <c r="P13">
+        <v>0.4676</v>
+      </c>
+      <c r="Q13">
+        <v>0.006318918918918919</v>
+      </c>
+      <c r="R13">
+        <v>-0.1553488372093023</v>
+      </c>
+      <c r="S13">
+        <v>1.54</v>
+      </c>
+      <c r="T13">
+        <v>0.7670850767085077</v>
+      </c>
+      <c r="U13">
+        <v>5.42</v>
+      </c>
+      <c r="V13">
+        <v>0.07324324324324324</v>
+      </c>
+      <c r="W13">
+        <v>-0.02675555555555555</v>
+      </c>
+      <c r="X13">
+        <v>0.06464398664639279</v>
+      </c>
+      <c r="Y13">
+        <v>-0.09139954220194835</v>
+      </c>
+      <c r="Z13">
+        <v>0.7022396373554608</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.05229996904215231</v>
+      </c>
+      <c r="AC13">
+        <v>-0.05229996904215231</v>
+      </c>
+      <c r="AD13">
+        <v>140.1</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>140.1</v>
+      </c>
+      <c r="AG13">
+        <v>134.68</v>
+      </c>
+      <c r="AH13">
+        <v>0.6543671181690799</v>
+      </c>
+      <c r="AI13">
+        <v>0.6078091106290672</v>
+      </c>
+      <c r="AJ13">
+        <v>0.6453900709219859</v>
+      </c>
+      <c r="AK13">
+        <v>0.5983650257686156</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>-1.04</v>
+      </c>
+      <c r="AQ13">
         <v>-0</v>
-      </c>
-      <c r="H13">
-        <v>-0</v>
-      </c>
-      <c r="I13">
-        <v>-0</v>
-      </c>
-      <c r="J13">
-        <v>-0</v>
-      </c>
-      <c r="K13">
-        <v>397.4</v>
-      </c>
-      <c r="L13">
-        <v>-14.82835820895522</v>
-      </c>
-      <c r="M13">
-        <v>162.184</v>
-      </c>
-      <c r="N13">
-        <v>0.05743873069839921</v>
-      </c>
-      <c r="O13">
-        <v>0.4081127327629592</v>
-      </c>
-      <c r="P13">
-        <v>162.184</v>
-      </c>
-      <c r="Q13">
-        <v>0.05743873069839921</v>
-      </c>
-      <c r="R13">
-        <v>0.4081127327629592</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>678.7</v>
-      </c>
-      <c r="V13">
-        <v>0.2403669074939793</v>
-      </c>
-      <c r="W13">
-        <v>0.06560678850312845</v>
-      </c>
-      <c r="X13">
-        <v>0.05548785381692333</v>
-      </c>
-      <c r="Y13">
-        <v>0.01011893468620512</v>
-      </c>
-      <c r="Z13">
-        <v>-0.001568462204742843</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0.02669290845059997</v>
-      </c>
-      <c r="AC13">
-        <v>-0.02669290845059997</v>
-      </c>
-      <c r="AD13">
-        <v>13512.8</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>13512.8</v>
-      </c>
-      <c r="AG13">
-        <v>12834.1</v>
-      </c>
-      <c r="AH13">
-        <v>0.8271589823951421</v>
-      </c>
-      <c r="AI13">
-        <v>0.683379270235416</v>
-      </c>
-      <c r="AJ13">
-        <v>0.8196670009005154</v>
-      </c>
-      <c r="AK13">
-        <v>0.672125395395605</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2073,7 +2079,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Han Kook Capital.Co., Ltd (KOSDAQ:A023760)</t>
+          <t>Meritz Financial Group Inc. (KOSE:A138040)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2082,10 +2088,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.189</v>
+        <v>0.132</v>
       </c>
       <c r="E14">
-        <v>0.243</v>
+        <v>0.252</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2100,82 +2106,85 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>37.3</v>
+        <v>757.4</v>
       </c>
       <c r="L14">
-        <v>0.4015069967707212</v>
+        <v>0.06347211048538483</v>
       </c>
       <c r="M14">
-        <v>-0</v>
+        <v>120.185</v>
       </c>
       <c r="N14">
-        <v>-0</v>
+        <v>0.02904071523498852</v>
       </c>
       <c r="O14">
-        <v>-0</v>
+        <v>0.1586810139952469</v>
       </c>
       <c r="P14">
-        <v>-0</v>
+        <v>17.885</v>
       </c>
       <c r="Q14">
-        <v>-0</v>
+        <v>0.004321614111393016</v>
       </c>
       <c r="R14">
-        <v>-0</v>
+        <v>0.02361367837338262</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>102.3</v>
+      </c>
+      <c r="T14">
+        <v>0.8511877522153348</v>
       </c>
       <c r="U14">
-        <v>284.4</v>
+        <v>3858.9</v>
       </c>
       <c r="V14">
-        <v>1.285714285714286</v>
+        <v>0.9324392895976803</v>
       </c>
       <c r="W14">
-        <v>0.1445176288260364</v>
+        <v>0.2459729799948039</v>
       </c>
       <c r="X14">
-        <v>0.09353898101117328</v>
+        <v>0.1257424194563558</v>
       </c>
       <c r="Y14">
-        <v>0.05097864781486311</v>
+        <v>0.1202305605384481</v>
       </c>
       <c r="Z14">
-        <v>0.05062946209602703</v>
+        <v>0.2755314801088937</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.02698412893408484</v>
+        <v>0.05338000646841085</v>
       </c>
       <c r="AC14">
-        <v>-0.02698412893408484</v>
+        <v>-0.05338000646841085</v>
       </c>
       <c r="AD14">
-        <v>2333.8</v>
+        <v>39403.8</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>2333.8</v>
+        <v>39403.8</v>
       </c>
       <c r="AG14">
-        <v>2049.4</v>
+        <v>35544.9</v>
       </c>
       <c r="AH14">
-        <v>0.9134246575342466</v>
+        <v>0.9049544925279556</v>
       </c>
       <c r="AI14">
-        <v>0.8770387072529126</v>
+        <v>0.9106683522421312</v>
       </c>
       <c r="AJ14">
-        <v>0.9025808156434424</v>
+        <v>0.8957120609625183</v>
       </c>
       <c r="AK14">
-        <v>0.8623243288731802</v>
+        <v>0.9019213300110123</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2192,7 +2201,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CNH Co., Ltd. (KOSDAQ:A023460)</t>
+          <t>Mirae Asset Securities Co. Ltd. (KOSE:A006800)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2201,10 +2210,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.365</v>
+        <v>0.159</v>
       </c>
       <c r="E15">
-        <v>0.606</v>
+        <v>0.198</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2219,94 +2228,91 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>19.8</v>
+        <v>505.6</v>
       </c>
       <c r="L15">
-        <v>0.07525655644241733</v>
+        <v>0.04335485641276293</v>
       </c>
       <c r="M15">
-        <v>1.4616</v>
+        <v>255</v>
       </c>
       <c r="N15">
-        <v>0.01964516129032258</v>
+        <v>0.0964374858180168</v>
       </c>
       <c r="O15">
-        <v>0.07381818181818181</v>
+        <v>0.5043512658227848</v>
       </c>
       <c r="P15">
-        <v>1.4616</v>
+        <v>132</v>
       </c>
       <c r="Q15">
-        <v>0.01964516129032258</v>
+        <v>0.04992058089403222</v>
       </c>
       <c r="R15">
-        <v>0.07381818181818181</v>
+        <v>0.2610759493670886</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>0.4823529411764706</v>
       </c>
       <c r="U15">
-        <v>27.5</v>
+        <v>2497.2</v>
       </c>
       <c r="V15">
-        <v>0.3696236559139784</v>
+        <v>0.944406625822555</v>
       </c>
       <c r="W15">
-        <v>0.2037037037037037</v>
+        <v>0.05694270815735829</v>
       </c>
       <c r="X15">
-        <v>0.03961198504517713</v>
+        <v>0.1944289119377287</v>
       </c>
       <c r="Y15">
-        <v>0.1640917186585266</v>
+        <v>-0.1374862037803704</v>
       </c>
       <c r="Z15">
-        <v>1.118527336110875</v>
+        <v>0.2200084517777031</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.02871654860629531</v>
+        <v>0.05626471901266216</v>
       </c>
       <c r="AC15">
-        <v>-0.02871654860629531</v>
+        <v>-0.05626471901266216</v>
       </c>
       <c r="AD15">
-        <v>177.1</v>
+        <v>47851.2</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>177.1</v>
+        <v>47851.2</v>
       </c>
       <c r="AG15">
-        <v>149.6</v>
+        <v>45354</v>
       </c>
       <c r="AH15">
-        <v>0.7041749502982108</v>
+        <v>0.947634834064093</v>
       </c>
       <c r="AI15">
-        <v>0.5981087470449172</v>
+        <v>0.8620999037931445</v>
       </c>
       <c r="AJ15">
-        <v>0.6678571428571428</v>
+        <v>0.9449104341412804</v>
       </c>
       <c r="AK15">
-        <v>0.5569620253164557</v>
+        <v>0.8556034726702662</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1.19</v>
-      </c>
-      <c r="AQ15">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2317,7 +2323,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Meritz Financial Group Inc. (KOSE:A138040)</t>
+          <t>IBKS No.15 Special Purpose Acquisition Company (KOSDAQ:A373200)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2325,455 +2331,71 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D16">
-        <v>0.122</v>
-      </c>
-      <c r="E16">
-        <v>0.241</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
       <c r="K16">
-        <v>601.9</v>
-      </c>
-      <c r="L16">
-        <v>0.04569506760501362</v>
+        <v>-0.053</v>
       </c>
       <c r="M16">
-        <v>183.2904</v>
+        <v>-0</v>
       </c>
       <c r="N16">
-        <v>0.03924595850373638</v>
+        <v>-0</v>
       </c>
       <c r="O16">
-        <v>0.3045196876557568</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>96.19040000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q16">
-        <v>0.02059619296404942</v>
+        <v>-0</v>
       </c>
       <c r="R16">
-        <v>0.1598112643296229</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="T16">
-        <v>0.475202192804424</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>3368.1</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>0.721174228636276</v>
-      </c>
-      <c r="W16">
-        <v>0.2132582199546485</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>0.08551524103656155</v>
-      </c>
-      <c r="Y16">
-        <v>0.1277429789180869</v>
-      </c>
-      <c r="Z16">
-        <v>0.3469766216661179</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
+        <v>0.04947963150541988</v>
       </c>
       <c r="AB16">
-        <v>0.03007800787688097</v>
-      </c>
-      <c r="AC16">
-        <v>-0.03007800787688097</v>
+        <v>0.04947963150541988</v>
       </c>
       <c r="AD16">
-        <v>43597.2</v>
+        <v>0</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>43597.2</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>40229.1</v>
+        <v>0</v>
       </c>
       <c r="AH16">
-        <v>0.903241311441446</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>0.8832513842207946</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>0.8959830198176367</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>0.8747015772376816</v>
+        <v>0</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
         <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Mirae Asset Securities Co., Ltd. (KOSE:A006800)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>0.198</v>
-      </c>
-      <c r="E17">
-        <v>1.009</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>982</v>
-      </c>
-      <c r="L17">
-        <v>0.09531204503542658</v>
-      </c>
-      <c r="M17">
-        <v>264</v>
-      </c>
-      <c r="N17">
-        <v>0.06321082245899677</v>
-      </c>
-      <c r="O17">
-        <v>0.2688391038696538</v>
-      </c>
-      <c r="P17">
-        <v>114.3</v>
-      </c>
-      <c r="Q17">
-        <v>0.02736741290554292</v>
-      </c>
-      <c r="R17">
-        <v>0.1163951120162933</v>
-      </c>
-      <c r="S17">
-        <v>149.7</v>
-      </c>
-      <c r="T17">
-        <v>0.5670454545454545</v>
-      </c>
-      <c r="U17">
-        <v>2355.7</v>
-      </c>
-      <c r="V17">
-        <v>0.5640368729797677</v>
-      </c>
-      <c r="W17">
-        <v>0.1203018572058607</v>
-      </c>
-      <c r="X17">
-        <v>0.0978928640455686</v>
-      </c>
-      <c r="Y17">
-        <v>0.02240899316029213</v>
-      </c>
-      <c r="Z17">
-        <v>0.1333892628310942</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>0.03227754241317814</v>
-      </c>
-      <c r="AC17">
-        <v>-0.03227754241317814</v>
-      </c>
-      <c r="AD17">
-        <v>46819.7</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>46819.7</v>
-      </c>
-      <c r="AG17">
-        <v>44464</v>
-      </c>
-      <c r="AH17">
-        <v>0.9181017409140289</v>
-      </c>
-      <c r="AI17">
-        <v>0.839401192237013</v>
-      </c>
-      <c r="AJ17">
-        <v>0.9141353398916541</v>
-      </c>
-      <c r="AK17">
-        <v>0.8323193902114866</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Korea Ratings Co., Ltd. (KOSDAQ:A034950)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>0.0684</v>
-      </c>
-      <c r="E18">
-        <v>0.104</v>
-      </c>
-      <c r="G18">
-        <v>0.3818959537572254</v>
-      </c>
-      <c r="H18">
-        <v>0.3815028901734104</v>
-      </c>
-      <c r="I18">
-        <v>0.3526011560693642</v>
-      </c>
-      <c r="J18">
-        <v>0.2552377400708559</v>
-      </c>
-      <c r="K18">
-        <v>18.7</v>
-      </c>
-      <c r="L18">
-        <v>0.2161849710982659</v>
-      </c>
-      <c r="M18">
-        <v>10.9716</v>
-      </c>
-      <c r="N18">
-        <v>0.03812230715774843</v>
-      </c>
-      <c r="O18">
-        <v>0.586716577540107</v>
-      </c>
-      <c r="P18">
-        <v>10.9716</v>
-      </c>
-      <c r="Q18">
-        <v>0.03812230715774843</v>
-      </c>
-      <c r="R18">
-        <v>0.586716577540107</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>91.7</v>
-      </c>
-      <c r="V18">
-        <v>0.3186240444753301</v>
-      </c>
-      <c r="W18">
-        <v>0.2493333333333333</v>
-      </c>
-      <c r="X18">
-        <v>0.02392039980770229</v>
-      </c>
-      <c r="Y18">
-        <v>0.225412933525631</v>
-      </c>
-      <c r="Z18">
-        <v>-23.76373626373626</v>
-      </c>
-      <c r="AA18">
-        <v>-6.065402339595887</v>
-      </c>
-      <c r="AB18">
-        <v>0.02391066655755508</v>
-      </c>
-      <c r="AC18">
-        <v>-6.089313006153442</v>
-      </c>
-      <c r="AD18">
-        <v>0.866</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
-      <c r="AF18">
-        <v>0.866</v>
-      </c>
-      <c r="AG18">
-        <v>-90.834</v>
-      </c>
-      <c r="AH18">
-        <v>0.003000006928422467</v>
-      </c>
-      <c r="AI18">
-        <v>0.008353751471070554</v>
-      </c>
-      <c r="AJ18">
-        <v>-0.4611658864981774</v>
-      </c>
-      <c r="AK18">
-        <v>-7.591007855590845</v>
-      </c>
-      <c r="AL18">
-        <v>0.039</v>
-      </c>
-      <c r="AM18">
-        <v>-0.9109999999999999</v>
-      </c>
-      <c r="AN18">
-        <v>0.02554572271386431</v>
-      </c>
-      <c r="AO18">
-        <v>782.0512820512821</v>
-      </c>
-      <c r="AP18">
-        <v>-2.679469026548673</v>
-      </c>
-      <c r="AQ18">
-        <v>-33.47969264544457</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>IBKS No.15 Special Purpose Acquisition Company (KOSDAQ:A373200)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="K19">
-        <v>-0.068</v>
-      </c>
-      <c r="M19">
-        <v>-0</v>
-      </c>
-      <c r="N19">
-        <v>-0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>-0</v>
-      </c>
-      <c r="Q19">
-        <v>-0</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>1.13</v>
-      </c>
-      <c r="V19">
-        <v>0.160968660968661</v>
-      </c>
-      <c r="X19">
-        <v>0.02483606634610229</v>
-      </c>
-      <c r="AB19">
-        <v>0.02503324558288245</v>
-      </c>
-      <c r="AD19">
-        <v>0.995</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
-      </c>
-      <c r="AF19">
-        <v>0.995</v>
-      </c>
-      <c r="AG19">
-        <v>-0.1349999999999999</v>
-      </c>
-      <c r="AH19">
-        <v>0.124142233312539</v>
-      </c>
-      <c r="AI19">
-        <v>0.1515613099771516</v>
-      </c>
-      <c r="AJ19">
-        <v>-0.01960784313725489</v>
-      </c>
-      <c r="AK19">
-        <v>-0.02483900643974239</v>
-      </c>
-      <c r="AL19">
-        <v>0.01</v>
-      </c>
-      <c r="AM19">
-        <v>0.01</v>
-      </c>
-      <c r="AO19">
-        <v>-6.600000000000001</v>
-      </c>
-      <c r="AQ19">
-        <v>-6.600000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/south_korea/south_korea_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ16"/>
+  <dimension ref="A1:AQ28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.107</v>
+        <v>0.0993</v>
       </c>
       <c r="E2">
-        <v>0.09570000000000001</v>
+        <v>0.0183</v>
+      </c>
+      <c r="F2">
+        <v>0.344</v>
       </c>
       <c r="G2">
-        <v>0.02024453286005512</v>
+        <v>0.02797455033661679</v>
       </c>
       <c r="H2">
-        <v>0.01934550734308201</v>
+        <v>0.02673237764277069</v>
       </c>
       <c r="I2">
-        <v>0.01169286750055079</v>
+        <v>0.01217457998589919</v>
       </c>
       <c r="J2">
-        <v>0.00943300364152635</v>
+        <v>0.01026700217419447</v>
       </c>
       <c r="K2">
-        <v>1865.26</v>
+        <v>2338.974</v>
       </c>
       <c r="L2">
-        <v>0.06929979071779746</v>
+        <v>0.08139542329222568</v>
       </c>
       <c r="M2">
-        <v>639.6458</v>
+        <v>637.35243</v>
       </c>
       <c r="N2">
-        <v>0.05770008208773465</v>
+        <v>0.02719699923105349</v>
       </c>
       <c r="O2">
-        <v>0.3429258119511489</v>
+        <v>0.2724923107311155</v>
       </c>
       <c r="P2">
-        <v>364.5058</v>
+        <v>386.64543</v>
       </c>
       <c r="Q2">
-        <v>0.03288072020711367</v>
+        <v>0.01649887090318358</v>
       </c>
       <c r="R2">
-        <v>0.1954182258773576</v>
+        <v>0.1653055698780748</v>
       </c>
       <c r="S2">
-        <v>275.14</v>
+        <v>250.707</v>
       </c>
       <c r="T2">
-        <v>0.4301443079904534</v>
+        <v>0.3933569375423892</v>
       </c>
       <c r="U2">
-        <v>8395.75</v>
+        <v>9591.342000000001</v>
       </c>
       <c r="V2">
-        <v>0.7573495584401526</v>
+        <v>0.4092801858443861</v>
       </c>
       <c r="W2">
-        <v>0.06105556990119101</v>
+        <v>0.08446906969897697</v>
       </c>
       <c r="X2">
-        <v>0.05435487386065301</v>
+        <v>0.05382693292917797</v>
       </c>
       <c r="Y2">
-        <v>0.006700696040538003</v>
+        <v>0.030642136769799</v>
       </c>
       <c r="Z2">
-        <v>0.2242416386837519</v>
+        <v>0.2540452341143643</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.06489757624645826</v>
       </c>
       <c r="AB2">
-        <v>0.0494782563520715</v>
+        <v>0.05154756979286279</v>
       </c>
       <c r="AC2">
-        <v>-0.04818974293868688</v>
+        <v>0.01473884299342913</v>
       </c>
       <c r="AD2">
-        <v>103598.816</v>
+        <v>113790.637</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>103598.816</v>
+        <v>113790.637</v>
       </c>
       <c r="AG2">
-        <v>95203.06600000001</v>
+        <v>104199.295</v>
       </c>
       <c r="AH2">
-        <v>0.9033374304862568</v>
+        <v>0.8292249278207064</v>
       </c>
       <c r="AI2">
-        <v>0.841733384143411</v>
+        <v>0.8055339739714804</v>
       </c>
       <c r="AJ2">
-        <v>0.8957020537805472</v>
+        <v>0.8163916490717537</v>
       </c>
       <c r="AK2">
-        <v>0.8301468695280303</v>
+        <v>0.7913683082265228</v>
       </c>
       <c r="AL2">
-        <v>52.452</v>
+        <v>120.603</v>
       </c>
       <c r="AM2">
-        <v>42.124</v>
+        <v>45.11500000000001</v>
       </c>
       <c r="AN2">
-        <v>222.4534925168023</v>
+        <v>180.2623952475248</v>
       </c>
       <c r="AO2">
-        <v>6.000209715549455</v>
+        <v>2.90082336260292</v>
       </c>
       <c r="AP2">
-        <v>204.4256425672629</v>
+        <v>165.0681900990099</v>
       </c>
       <c r="AQ2">
-        <v>7.471346500807142</v>
+        <v>7.754582733015625</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Korea Ratings Co., Ltd. (KOSDAQ:A034950)</t>
+          <t>Koramco Life Infra Reit Co.,Ltd (KOSE:A357120)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,113 +724,98 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.0572</v>
-      </c>
-      <c r="E3">
-        <v>0.0706</v>
-      </c>
       <c r="G3">
-        <v>0.4712482853223594</v>
+        <v>0.8252788104089219</v>
       </c>
       <c r="H3">
-        <v>0.4705075445816186</v>
+        <v>0.8252788104089219</v>
       </c>
       <c r="I3">
-        <v>0.3278463648834019</v>
+        <v>0.7137546468401487</v>
       </c>
       <c r="J3">
-        <v>0.2347379972565157</v>
+        <v>0.7137546468401487</v>
       </c>
       <c r="K3">
-        <v>14.7</v>
+        <v>20.7</v>
       </c>
       <c r="L3">
-        <v>0.2016460905349794</v>
+        <v>0.3847583643122677</v>
       </c>
       <c r="M3">
-        <v>10.5702</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.0434094455852156</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.7190612244897959</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>10.5702</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.0434094455852156</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.7190612244897959</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>75.3</v>
+        <v>25.6</v>
       </c>
       <c r="V3">
-        <v>0.3092402464065708</v>
-      </c>
-      <c r="W3">
-        <v>0.1719298245614035</v>
+        <v>0.07211267605633803</v>
       </c>
       <c r="X3">
-        <v>0.04949469702255381</v>
-      </c>
-      <c r="Y3">
-        <v>0.1224351275388497</v>
+        <v>0.06565147449943882</v>
       </c>
       <c r="AB3">
-        <v>0.0494768811987231</v>
+        <v>0.0528514742151471</v>
       </c>
       <c r="AD3">
-        <v>0.458</v>
+        <v>523.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.458</v>
+        <v>523.8</v>
       </c>
       <c r="AG3">
-        <v>-74.842</v>
+        <v>498.1999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.001877372334582182</v>
+        <v>0.5960400546199363</v>
       </c>
       <c r="AI3">
-        <v>0.005608758480491807</v>
+        <v>0.6071635562768054</v>
       </c>
       <c r="AJ3">
-        <v>-0.4437500741144801</v>
+        <v>0.583919362400375</v>
       </c>
       <c r="AK3">
-        <v>-11.77131173324944</v>
+        <v>0.5951499223509736</v>
       </c>
       <c r="AL3">
-        <v>0.019</v>
+        <v>18.5</v>
       </c>
       <c r="AM3">
-        <v>-0.465</v>
+        <v>17.799</v>
       </c>
       <c r="AN3">
-        <v>0.01635714285714286</v>
+        <v>11.7972972972973</v>
       </c>
       <c r="AO3">
-        <v>1257.894736842105</v>
+        <v>2.075675675675676</v>
       </c>
       <c r="AP3">
-        <v>-2.672928571428571</v>
+        <v>11.22072072072072</v>
       </c>
       <c r="AQ3">
-        <v>-51.39784946236559</v>
+        <v>2.157424574414293</v>
       </c>
     </row>
     <row r="4">
@@ -838,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>COOCON Corporation (KOSDAQ:A294570)</t>
+          <t>Hecto Financial Co., Ltd. (KOSDAQ:A234340)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -847,115 +835,106 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.4845474613686535</v>
+        <v>0.1283005366726297</v>
       </c>
       <c r="H4">
-        <v>0.3929359823399559</v>
+        <v>0.1207513416815742</v>
       </c>
       <c r="I4">
-        <v>0.304635761589404</v>
+        <v>0.08255813953488372</v>
       </c>
       <c r="J4">
-        <v>0.2648201453330382</v>
+        <v>0.06107185450208707</v>
       </c>
       <c r="K4">
-        <v>0.76</v>
+        <v>11.7</v>
       </c>
       <c r="L4">
-        <v>0.01677704194260486</v>
+        <v>0.1046511627906977</v>
       </c>
       <c r="M4">
-        <v>0.714</v>
+        <v>6.799300000000001</v>
       </c>
       <c r="N4">
-        <v>0.002692307692307692</v>
+        <v>0.03948490127758421</v>
       </c>
       <c r="O4">
-        <v>0.9394736842105262</v>
+        <v>0.5811367521367522</v>
       </c>
       <c r="P4">
-        <v>0.714</v>
+        <v>3.0793</v>
       </c>
       <c r="Q4">
-        <v>0.002692307692307692</v>
+        <v>0.01788211382113821</v>
       </c>
       <c r="R4">
-        <v>0.9394736842105262</v>
+        <v>0.2631880341880342</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.5471151442060211</v>
       </c>
       <c r="U4">
-        <v>54.6</v>
+        <v>101.6</v>
       </c>
       <c r="V4">
-        <v>0.2058823529411765</v>
+        <v>0.5900116144018583</v>
       </c>
       <c r="W4">
-        <v>0.006877828054298643</v>
+        <v>0.1266233766233766</v>
       </c>
       <c r="X4">
-        <v>0.04949902156035903</v>
+        <v>0.05167947307120005</v>
       </c>
       <c r="Y4">
-        <v>-0.04262119350606038</v>
-      </c>
-      <c r="Z4">
-        <v>1.039229181004818</v>
-      </c>
-      <c r="AA4">
-        <v>0.27520882274803</v>
+        <v>0.07494390355217656</v>
       </c>
       <c r="AB4">
-        <v>0.04949004007505549</v>
-      </c>
-      <c r="AC4">
-        <v>0.2257187826729745</v>
+        <v>0.05154882268126018</v>
       </c>
       <c r="AD4">
-        <v>0.642</v>
+        <v>2.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.642</v>
+        <v>2.4</v>
       </c>
       <c r="AG4">
-        <v>-53.958</v>
+        <v>-99.19999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.002414968289435078</v>
+        <v>0.01374570446735395</v>
       </c>
       <c r="AI4">
-        <v>0.007082809293704906</v>
+        <v>0.02183803457688808</v>
       </c>
       <c r="AJ4">
-        <v>-0.2554321583775954</v>
+        <v>-1.358904109589041</v>
       </c>
       <c r="AK4">
-        <v>-1.49708673214583</v>
+        <v>-11.95180722891564</v>
       </c>
       <c r="AL4">
-        <v>0.026</v>
+        <v>0.144</v>
       </c>
       <c r="AM4">
-        <v>-0.322</v>
+        <v>-1.756</v>
       </c>
       <c r="AN4">
-        <v>0.03732558139534884</v>
+        <v>0.183206106870229</v>
       </c>
       <c r="AO4">
-        <v>530.7692307692308</v>
+        <v>64.09722222222223</v>
       </c>
       <c r="AP4">
-        <v>-3.137093023255814</v>
+        <v>-7.572519083969465</v>
       </c>
       <c r="AQ4">
-        <v>-42.85714285714287</v>
+        <v>-5.256264236902051</v>
       </c>
     </row>
     <row r="5">
@@ -966,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SCI Information Service Inc. (KOSDAQ:A036120)</t>
+          <t>Korea Ratings Co., Ltd. (KOSDAQ:A034950)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -975,46 +954,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0139</v>
+        <v>0.0257</v>
       </c>
       <c r="E5">
-        <v>1.173</v>
+        <v>0.0142</v>
       </c>
       <c r="G5">
-        <v>0.3475409836065574</v>
+        <v>0.4110503597122303</v>
       </c>
       <c r="H5">
-        <v>0.3475409836065574</v>
+        <v>0.4100719424460432</v>
       </c>
       <c r="I5">
-        <v>0.1524590163934426</v>
+        <v>0.2316546762589928</v>
       </c>
       <c r="J5">
-        <v>0.1223204000253181</v>
+        <v>0.1964728965490709</v>
       </c>
       <c r="K5">
-        <v>2.12</v>
+        <v>13.4</v>
       </c>
       <c r="L5">
-        <v>0.06950819672131148</v>
+        <v>0.1928057553956835</v>
       </c>
       <c r="M5">
-        <v>0.9688000000000001</v>
+        <v>21.4526</v>
       </c>
       <c r="N5">
-        <v>0.008945521698984304</v>
+        <v>0.08101435045317219</v>
       </c>
       <c r="O5">
-        <v>0.4569811320754718</v>
+        <v>1.600940298507462</v>
       </c>
       <c r="P5">
-        <v>0.9688000000000001</v>
+        <v>21.4526</v>
       </c>
       <c r="Q5">
-        <v>0.008945521698984304</v>
+        <v>0.08101435045317219</v>
       </c>
       <c r="R5">
-        <v>0.4569811320754718</v>
+        <v>1.600940298507462</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1023,67 +1002,64 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>7.48</v>
+        <v>71</v>
       </c>
       <c r="V5">
-        <v>0.06906740535549401</v>
+        <v>0.2681268882175227</v>
       </c>
       <c r="W5">
-        <v>0.08249027237354087</v>
+        <v>0.1887323943661972</v>
       </c>
       <c r="X5">
-        <v>0.04951409624421162</v>
+        <v>0.05161230289241883</v>
       </c>
       <c r="Y5">
-        <v>0.03297617612932925</v>
-      </c>
-      <c r="Z5">
-        <v>1.467616206332403</v>
-      </c>
-      <c r="AA5">
-        <v>0.1795194014422193</v>
+        <v>0.1371200914737783</v>
       </c>
       <c r="AB5">
-        <v>0.04951030810348728</v>
-      </c>
-      <c r="AC5">
-        <v>0.130009093338732</v>
+        <v>0.05151761039115679</v>
       </c>
       <c r="AD5">
-        <v>0.466</v>
+        <v>1.83</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.466</v>
+        <v>1.83</v>
       </c>
       <c r="AG5">
-        <v>-7.014</v>
+        <v>-69.17</v>
       </c>
       <c r="AH5">
-        <v>0.004284427118768733</v>
+        <v>0.006863443723511983</v>
       </c>
       <c r="AI5">
-        <v>0.02046912061846613</v>
+        <v>0.02157255687846281</v>
       </c>
       <c r="AJ5">
-        <v>-0.0692494520466797</v>
+        <v>-0.353575627460001</v>
       </c>
       <c r="AK5">
-        <v>-0.4588512364254874</v>
+        <v>-5.001446131597977</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>-1.632</v>
       </c>
       <c r="AN5">
-        <v>0.0762684124386252</v>
+        <v>0.09059405940594061</v>
+      </c>
+      <c r="AO5">
+        <v>894.4444444444446</v>
       </c>
       <c r="AP5">
-        <v>-1.147954173486088</v>
+        <v>-3.424257425742574</v>
+      </c>
+      <c r="AQ5">
+        <v>-9.865196078431374</v>
       </c>
     </row>
     <row r="6">
@@ -1094,7 +1070,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The LEADCORP, Inc. (KOSDAQ:A012700)</t>
+          <t>NHN KCP Corp. (KOSDAQ:A060250)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1103,46 +1079,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0728</v>
+        <v>0.178</v>
       </c>
       <c r="E6">
-        <v>0.07200000000000001</v>
+        <v>0.229</v>
       </c>
       <c r="G6">
-        <v>0.1903052064631957</v>
+        <v>0.05956673451584763</v>
       </c>
       <c r="H6">
-        <v>0.1903052064631957</v>
+        <v>0.05612096539691772</v>
       </c>
       <c r="I6">
-        <v>0.1600089766606822</v>
+        <v>0.04434428612968887</v>
       </c>
       <c r="J6">
-        <v>0.1211496537573737</v>
+        <v>0.03290743143833031</v>
       </c>
       <c r="K6">
-        <v>31.8</v>
+        <v>24.9</v>
       </c>
       <c r="L6">
-        <v>0.07136445242369838</v>
+        <v>0.03620238441407386</v>
       </c>
       <c r="M6">
-        <v>14.2592</v>
+        <v>5.7663</v>
       </c>
       <c r="N6">
-        <v>0.09557104557640753</v>
+        <v>0.01867325129533679</v>
       </c>
       <c r="O6">
-        <v>0.4484025157232705</v>
+        <v>0.2315783132530121</v>
       </c>
       <c r="P6">
-        <v>14.2592</v>
+        <v>5.7663</v>
       </c>
       <c r="Q6">
-        <v>0.09557104557640753</v>
+        <v>0.01867325129533679</v>
       </c>
       <c r="R6">
-        <v>0.4484025157232705</v>
+        <v>0.2315783132530121</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1151,73 +1127,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>23.5</v>
+        <v>176.8</v>
       </c>
       <c r="V6">
-        <v>0.1575067024128687</v>
+        <v>0.572538860103627</v>
       </c>
       <c r="W6">
-        <v>0.09054669703872438</v>
+        <v>0.1873589164785553</v>
       </c>
       <c r="X6">
-        <v>0.05302280683731187</v>
+        <v>0.05155029257616514</v>
       </c>
       <c r="Y6">
-        <v>0.03752389020141251</v>
+        <v>0.1358086239023902</v>
       </c>
       <c r="Z6">
-        <v>1.08392118705911</v>
+        <v>30.88459811405476</v>
       </c>
       <c r="AA6">
-        <v>0.1313166765124926</v>
+        <v>1.016332794938643</v>
       </c>
       <c r="AB6">
-        <v>0.04903033568235376</v>
+        <v>0.0515463169044654</v>
       </c>
       <c r="AC6">
-        <v>0.08228634083013883</v>
+        <v>0.9647864780341773</v>
       </c>
       <c r="AD6">
-        <v>66</v>
+        <v>0.131</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>66</v>
+        <v>0.131</v>
       </c>
       <c r="AG6">
-        <v>42.5</v>
+        <v>-176.669</v>
       </c>
       <c r="AH6">
-        <v>0.3066914498141264</v>
+        <v>0.0004240429092580544</v>
       </c>
       <c r="AI6">
-        <v>0.1763291477424526</v>
+        <v>0.0008140134591843709</v>
       </c>
       <c r="AJ6">
-        <v>0.2217005738132499</v>
+        <v>-1.337074569934383</v>
       </c>
       <c r="AK6">
-        <v>0.12115165336374</v>
+        <v>11.13296363980087</v>
       </c>
       <c r="AL6">
-        <v>30.2</v>
+        <v>0.164</v>
       </c>
       <c r="AM6">
-        <v>30.037</v>
+        <v>-1.536</v>
       </c>
       <c r="AN6">
-        <v>0.8906882591093118</v>
+        <v>0.003841642228739003</v>
       </c>
       <c r="AO6">
-        <v>2.360927152317881</v>
+        <v>185.9756097560976</v>
       </c>
       <c r="AP6">
-        <v>0.5735492577597842</v>
+        <v>-5.180909090909091</v>
       </c>
       <c r="AQ6">
-        <v>2.373739055165296</v>
+        <v>-19.85677083333333</v>
       </c>
     </row>
     <row r="7">
@@ -1228,7 +1204,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NICE Holdings Co., Ltd. (KOSE:A034310)</t>
+          <t>Nice Information &amp; Telecommunication, Inc. (KOSDAQ:A036800)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1237,121 +1213,121 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.145</v>
+        <v>0.165</v>
       </c>
       <c r="E7">
-        <v>-0.011</v>
+        <v>-0.0141</v>
       </c>
       <c r="G7">
-        <v>0.1416881111682965</v>
+        <v>0.08835341365461848</v>
       </c>
       <c r="H7">
-        <v>0.131497683993824</v>
+        <v>0.08835341365461848</v>
       </c>
       <c r="I7">
-        <v>0.0626865671641791</v>
+        <v>0.0458758109360519</v>
       </c>
       <c r="J7">
-        <v>0.04110804506578445</v>
+        <v>0.03548185854785387</v>
       </c>
       <c r="K7">
-        <v>32.7</v>
+        <v>26.4</v>
       </c>
       <c r="L7">
-        <v>0.01682964487905301</v>
+        <v>0.04077849860982391</v>
       </c>
       <c r="M7">
-        <v>57.6177</v>
+        <v>10.49183</v>
       </c>
       <c r="N7">
-        <v>0.1581166300768387</v>
+        <v>0.06952836315440689</v>
       </c>
       <c r="O7">
-        <v>1.762009174311926</v>
+        <v>0.3974178030303031</v>
       </c>
       <c r="P7">
-        <v>9.3177</v>
+        <v>4.35183</v>
       </c>
       <c r="Q7">
-        <v>0.02556997804610319</v>
+        <v>0.02883916500994035</v>
       </c>
       <c r="R7">
-        <v>0.2849449541284403</v>
+        <v>0.1648420454545454</v>
       </c>
       <c r="S7">
-        <v>48.3</v>
+        <v>6.140000000000001</v>
       </c>
       <c r="T7">
-        <v>0.8382840689579765</v>
+        <v>0.5852172595247922</v>
       </c>
       <c r="U7">
-        <v>393.1</v>
+        <v>209.8</v>
       </c>
       <c r="V7">
-        <v>1.078759604829857</v>
+        <v>1.390324718356527</v>
       </c>
       <c r="W7">
-        <v>0.05178967374089326</v>
+        <v>0.1222222222222222</v>
       </c>
       <c r="X7">
-        <v>0.06523970791057779</v>
+        <v>0.05226843944620135</v>
       </c>
       <c r="Y7">
-        <v>-0.01345003416968453</v>
+        <v>0.06995378277602086</v>
       </c>
       <c r="Z7">
-        <v>2.613666935700834</v>
+        <v>10.71854304635761</v>
       </c>
       <c r="AA7">
-        <v>0.1074427381797407</v>
+        <v>0.3803138282099435</v>
       </c>
       <c r="AB7">
-        <v>0.04850830888454981</v>
+        <v>0.05125327174705382</v>
       </c>
       <c r="AC7">
-        <v>0.05893442929519085</v>
+        <v>0.3290605564628897</v>
       </c>
       <c r="AD7">
-        <v>717</v>
+        <v>11.4</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>717</v>
+        <v>11.4</v>
       </c>
       <c r="AG7">
-        <v>323.9</v>
+        <v>-198.4</v>
       </c>
       <c r="AH7">
-        <v>0.6630294063251341</v>
+        <v>0.07024029574861368</v>
       </c>
       <c r="AI7">
-        <v>0.4366094263792473</v>
+        <v>0.04065620542082739</v>
       </c>
       <c r="AJ7">
-        <v>0.47057968908906</v>
+        <v>4.176842105263158</v>
       </c>
       <c r="AK7">
-        <v>0.2593067008245937</v>
+        <v>-2.810198300283286</v>
       </c>
       <c r="AL7">
-        <v>19.9</v>
+        <v>0.672</v>
       </c>
       <c r="AM7">
-        <v>12.43</v>
+        <v>-5.048</v>
       </c>
       <c r="AN7">
-        <v>2.819504522217853</v>
+        <v>0.2298387096774193</v>
       </c>
       <c r="AO7">
-        <v>6.120603015075377</v>
+        <v>44.19642857142857</v>
       </c>
       <c r="AP7">
-        <v>1.273692489186001</v>
+        <v>-4</v>
       </c>
       <c r="AQ7">
-        <v>9.798873692679003</v>
+        <v>-5.883518225039619</v>
       </c>
     </row>
     <row r="8">
@@ -1362,7 +1338,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sangsangin Co., Ltd. (KOSDAQ:A038540)</t>
+          <t>COOCON Corporation (KOSDAQ:A294570)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1370,122 +1346,116 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D8">
-        <v>0.107</v>
-      </c>
-      <c r="E8">
-        <v>0.0024</v>
-      </c>
       <c r="G8">
-        <v>0.2432308644522385</v>
+        <v>0.4798780487804878</v>
       </c>
       <c r="H8">
-        <v>0.2428306168764184</v>
+        <v>0.4024390243902439</v>
       </c>
       <c r="I8">
-        <v>0.1638126676294615</v>
+        <v>0.2764227642276422</v>
       </c>
       <c r="J8">
-        <v>0.1207464380561142</v>
+        <v>0.2119241192411924</v>
       </c>
       <c r="K8">
-        <v>63</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L8">
-        <v>0.1299773055498246</v>
+        <v>0.1737804878048781</v>
       </c>
       <c r="M8">
-        <v>7.603300000000001</v>
+        <v>1.2078</v>
       </c>
       <c r="N8">
-        <v>0.02865925367508481</v>
+        <v>0.007553470919324578</v>
       </c>
       <c r="O8">
-        <v>0.1206873015873016</v>
+        <v>0.1412631578947368</v>
       </c>
       <c r="P8">
-        <v>7.603300000000001</v>
+        <v>0.7547999999999999</v>
       </c>
       <c r="Q8">
-        <v>0.02865925367508481</v>
+        <v>0.004720450281425891</v>
       </c>
       <c r="R8">
-        <v>0.1206873015873016</v>
+        <v>0.08828070175438595</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>0.4530000000000001</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.3750620963735719</v>
       </c>
       <c r="U8">
-        <v>185.2</v>
+        <v>55.3</v>
       </c>
       <c r="V8">
-        <v>0.6980776479457218</v>
+        <v>0.3458411507191995</v>
       </c>
       <c r="W8">
-        <v>0.1108374384236453</v>
+        <v>0.09542410714285715</v>
       </c>
       <c r="X8">
-        <v>0.05568694088399413</v>
+        <v>0.05187087160669448</v>
       </c>
       <c r="Y8">
-        <v>0.05515049753965119</v>
+        <v>0.04355323553616267</v>
       </c>
       <c r="Z8">
-        <v>0.7049156486329261</v>
+        <v>1.437671673192684</v>
       </c>
       <c r="AA8">
-        <v>0.08511605370244114</v>
+        <v>0.3046773030993709</v>
       </c>
       <c r="AB8">
-        <v>0.04884000694358601</v>
+        <v>0.05140925052031176</v>
       </c>
       <c r="AC8">
-        <v>0.03627604675885513</v>
+        <v>0.2532680525790591</v>
       </c>
       <c r="AD8">
-        <v>205.6</v>
+        <v>5.43</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>205.6</v>
+        <v>5.43</v>
       </c>
       <c r="AG8">
-        <v>20.40000000000001</v>
+        <v>-49.87</v>
       </c>
       <c r="AH8">
-        <v>0.436610745381185</v>
+        <v>0.03284340410088913</v>
       </c>
       <c r="AI8">
-        <v>0.2498177399756986</v>
+        <v>0.05087604234985477</v>
       </c>
       <c r="AJ8">
-        <v>0.07140357017850893</v>
+        <v>-0.4532400254476052</v>
       </c>
       <c r="AK8">
-        <v>0.03198494825964254</v>
+        <v>-0.9696675092358545</v>
       </c>
       <c r="AL8">
-        <v>2.22</v>
+        <v>0.13</v>
       </c>
       <c r="AM8">
-        <v>1.913</v>
+        <v>-0.352</v>
       </c>
       <c r="AN8">
-        <v>2.390697674418604</v>
+        <v>0.3138728323699422</v>
       </c>
       <c r="AO8">
-        <v>35.76576576576576</v>
+        <v>104.6153846153846</v>
       </c>
       <c r="AP8">
-        <v>0.2372093023255815</v>
+        <v>-2.882658959537572</v>
       </c>
       <c r="AQ8">
-        <v>41.5054887611082</v>
+        <v>-38.63636363636364</v>
       </c>
     </row>
     <row r="9">
@@ -1496,7 +1466,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Han Kook Capital.Co., Ltd (KOSDAQ:A023760)</t>
+          <t>Korea Information &amp; Communications Co., Ltd. (KOSDAQ:A025770)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1505,37 +1475,37 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.264</v>
+        <v>0.103</v>
       </c>
       <c r="E9">
-        <v>0.7020000000000001</v>
+        <v>0.0643</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>0.05208333333333333</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>0.05208333333333333</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>0.05188679245283018</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>0.04171837406610104</v>
       </c>
       <c r="K9">
-        <v>53.4</v>
+        <v>24.2</v>
       </c>
       <c r="L9">
-        <v>0.4881170018281535</v>
+        <v>0.047562893081761</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>1.5</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.005673222390317701</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0.06198347107438017</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1547,64 +1517,79 @@
         <v>-0</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.5</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
       </c>
       <c r="U9">
-        <v>360.3</v>
+        <v>61.2</v>
       </c>
       <c r="V9">
-        <v>1.953904555314534</v>
+        <v>0.2314674735249622</v>
       </c>
       <c r="W9">
-        <v>0.1632029339853301</v>
+        <v>0.1481028151774786</v>
       </c>
       <c r="X9">
-        <v>0.1435895404790209</v>
+        <v>0.05171617090206278</v>
       </c>
       <c r="Y9">
-        <v>0.01961339350630911</v>
+        <v>0.09638664427541578</v>
       </c>
       <c r="Z9">
-        <v>0.04603214676428512</v>
+        <v>6.339396959880387</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>0.2644693337257937</v>
       </c>
       <c r="AB9">
-        <v>0.04812955984106757</v>
+        <v>0.05154952239078354</v>
       </c>
       <c r="AC9">
-        <v>-0.04812955984106757</v>
+        <v>0.2129198113350102</v>
       </c>
       <c r="AD9">
-        <v>2166.6</v>
+        <v>4.7</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>2166.6</v>
+        <v>4.7</v>
       </c>
       <c r="AG9">
-        <v>1806.3</v>
+        <v>-56.5</v>
       </c>
       <c r="AH9">
-        <v>0.9215652913653763</v>
+        <v>0.01746562616127834</v>
       </c>
       <c r="AI9">
-        <v>0.8735233641091804</v>
+        <v>0.02257444764649376</v>
       </c>
       <c r="AJ9">
-        <v>0.9073692670919776</v>
+        <v>-0.2717652717652718</v>
       </c>
       <c r="AK9">
-        <v>0.8520283018867925</v>
+        <v>-0.3843537414965986</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>-3.47</v>
+      </c>
+      <c r="AN9">
+        <v>0.1398809523809524</v>
+      </c>
+      <c r="AO9">
+        <v>94.28571428571428</v>
+      </c>
+      <c r="AP9">
+        <v>-1.681547619047619</v>
+      </c>
+      <c r="AQ9">
+        <v>-7.60806916426513</v>
       </c>
     </row>
     <row r="10">
@@ -1615,7 +1600,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Samsung Card Co., Ltd. (KOSE:A029780)</t>
+          <t>Kginicis Co.,Ltd (KOSDAQ:A035600)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1624,46 +1609,46 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.486</v>
+        <v>0.0732</v>
       </c>
       <c r="E10">
-        <v>0.09570000000000001</v>
+        <v>0.439</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>0.1238988580750408</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>0.1227569331158238</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>0.07718189233278956</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>0.06641181165483297</v>
       </c>
       <c r="K10">
-        <v>408</v>
+        <v>52.9</v>
       </c>
       <c r="L10">
-        <v>82.09255533199196</v>
+        <v>0.05393556280587276</v>
       </c>
       <c r="M10">
-        <v>170.72</v>
+        <v>7.9002</v>
       </c>
       <c r="N10">
-        <v>0.06844405243956221</v>
+        <v>0.03182997582594682</v>
       </c>
       <c r="O10">
-        <v>0.4184313725490197</v>
+        <v>0.1493421550094518</v>
       </c>
       <c r="P10">
-        <v>170.72</v>
+        <v>7.9002</v>
       </c>
       <c r="Q10">
-        <v>0.06844405243956221</v>
+        <v>0.03182997582594682</v>
       </c>
       <c r="R10">
-        <v>0.4184313725490197</v>
+        <v>0.1493421550094518</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1672,61 +1657,73 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>924.1</v>
+        <v>84.2</v>
       </c>
       <c r="V10">
-        <v>0.3704847051276911</v>
+        <v>0.339242546333602</v>
       </c>
       <c r="W10">
-        <v>0.06516843164502373</v>
+        <v>0.1962894248608534</v>
       </c>
       <c r="X10">
-        <v>0.09134451059954737</v>
+        <v>0.06147181725484187</v>
       </c>
       <c r="Y10">
-        <v>-0.02617607895452365</v>
+        <v>0.1348176076060116</v>
       </c>
       <c r="Z10">
-        <v>0.0002602802857322412</v>
+        <v>2.691547749725576</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>0.1787505622147645</v>
       </c>
       <c r="AB10">
-        <v>0.04824992603630619</v>
+        <v>0.04942162463705096</v>
       </c>
       <c r="AC10">
-        <v>-0.04824992603630619</v>
+        <v>0.1293289375777135</v>
       </c>
       <c r="AD10">
-        <v>13037.1</v>
+        <v>257.7</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>13037.1</v>
+        <v>257.7</v>
       </c>
       <c r="AG10">
-        <v>12113</v>
+        <v>173.5</v>
       </c>
       <c r="AH10">
-        <v>0.8394027582832198</v>
+        <v>0.5093892073532319</v>
       </c>
       <c r="AI10">
-        <v>0.7057801309015315</v>
+        <v>0.3423219978746015</v>
       </c>
       <c r="AJ10">
-        <v>0.8292429127901803</v>
+        <v>0.4114299264880247</v>
       </c>
       <c r="AK10">
-        <v>0.6902859617729858</v>
+        <v>0.2594974573736165</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>2.200000000000001</v>
+      </c>
+      <c r="AN10">
+        <v>2.355575868372943</v>
+      </c>
+      <c r="AO10">
+        <v>8.771726535341831</v>
+      </c>
+      <c r="AP10">
+        <v>1.585923217550274</v>
+      </c>
+      <c r="AQ10">
+        <v>34.40909090909089</v>
       </c>
     </row>
     <row r="11">
@@ -1737,7 +1734,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mason Capital Corporation (KOSDAQ:A021880)</t>
+          <t>Cubic Korea Inc. (KOSDAQ:A021650)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1746,103 +1743,121 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.204</v>
+        <v>0.09329999999999999</v>
+      </c>
+      <c r="E11">
+        <v>0.249</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>0.07154384077461001</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>0.07154384077461001</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>0.05040344271113501</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>0.04077412828273907</v>
       </c>
       <c r="K11">
-        <v>-1.46</v>
+        <v>5.43</v>
       </c>
       <c r="L11">
-        <v>-0.7525773195876289</v>
+        <v>0.02920925228617536</v>
       </c>
       <c r="M11">
-        <v>-0</v>
+        <v>0.7335</v>
       </c>
       <c r="N11">
-        <v>-0</v>
+        <v>0.020375</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>0.1350828729281768</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>0.7335</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>0.020375</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>0.1350828729281768</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
       <c r="U11">
-        <v>10.2</v>
+        <v>13.2</v>
       </c>
       <c r="V11">
-        <v>0.2524752475247525</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="W11">
-        <v>-0.03067226890756302</v>
+        <v>0.09926873857404021</v>
       </c>
       <c r="X11">
-        <v>0.05085952448706077</v>
+        <v>0.05667128666074254</v>
       </c>
       <c r="Y11">
-        <v>-0.0815317933946238</v>
+        <v>0.04259745191329768</v>
       </c>
       <c r="Z11">
-        <v>0.05350248207391064</v>
+        <v>2.659513590844063</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>0.1084393483227638</v>
       </c>
       <c r="AB11">
-        <v>0.05011303020224182</v>
+        <v>0.05009056968907906</v>
       </c>
       <c r="AC11">
-        <v>-0.05011303020224182</v>
+        <v>0.05834877863368479</v>
       </c>
       <c r="AD11">
-        <v>6.96</v>
+        <v>19.3</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>6.96</v>
+        <v>19.3</v>
       </c>
       <c r="AG11">
-        <v>-3.239999999999999</v>
+        <v>6.100000000000001</v>
       </c>
       <c r="AH11">
-        <v>0.1469594594594595</v>
+        <v>0.3490054249547921</v>
       </c>
       <c r="AI11">
-        <v>0.1517662450937636</v>
+        <v>0.2345078979343864</v>
       </c>
       <c r="AJ11">
-        <v>-0.08719052744886974</v>
+        <v>0.1448931116389549</v>
       </c>
       <c r="AK11">
-        <v>-0.09085810431856421</v>
+        <v>0.08827785817655574</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>0.846</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>0.592</v>
+      </c>
+      <c r="AN11">
+        <v>1.295302013422819</v>
+      </c>
+      <c r="AO11">
+        <v>11.07565011820331</v>
+      </c>
+      <c r="AP11">
+        <v>0.4093959731543625</v>
+      </c>
+      <c r="AQ11">
+        <v>15.8277027027027</v>
       </c>
     </row>
     <row r="12">
@@ -1853,7 +1868,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NH Special Purpose Acquisition 20 Company (KOSDAQ:A391060)</t>
+          <t>The LEADCORP, Inc. (KOSDAQ:A012700)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1861,92 +1876,122 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D12">
+        <v>0.04769999999999999</v>
+      </c>
+      <c r="E12">
+        <v>-0.309</v>
+      </c>
+      <c r="G12">
+        <v>0.2165922814386978</v>
+      </c>
+      <c r="H12">
+        <v>0.2165922814386978</v>
+      </c>
+      <c r="I12">
+        <v>0.1123654502494093</v>
+      </c>
+      <c r="J12">
+        <v>0.09012694360297088</v>
+      </c>
       <c r="K12">
-        <v>0.303</v>
+        <v>3.84</v>
+      </c>
+      <c r="L12">
+        <v>0.01008138619060121</v>
       </c>
       <c r="M12">
-        <v>-0</v>
+        <v>9.4976</v>
       </c>
       <c r="N12">
-        <v>-0</v>
+        <v>0.07816954732510288</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>2.473333333333334</v>
       </c>
       <c r="P12">
-        <v>-0</v>
+        <v>9.4976</v>
       </c>
       <c r="Q12">
-        <v>-0</v>
+        <v>0.07816954732510288</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>2.473333333333334</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
       <c r="U12">
-        <v>0.45</v>
+        <v>17.3</v>
       </c>
       <c r="V12">
-        <v>0.01139240506329114</v>
+        <v>0.1423868312757202</v>
       </c>
       <c r="W12">
-        <v>0.007890625</v>
+        <v>0.0124554005838469</v>
       </c>
       <c r="X12">
-        <v>0.05006565938612868</v>
+        <v>0.05638508642859923</v>
       </c>
       <c r="Y12">
-        <v>-0.04217503438612868</v>
+        <v>-0.04392968584475233</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1.085803876852907</v>
       </c>
       <c r="AA12">
-        <v>-0.001085688405277807</v>
+        <v>0.09786018477300913</v>
       </c>
       <c r="AB12">
-        <v>0.04937975458596065</v>
+        <v>0.05014454054133276</v>
       </c>
       <c r="AC12">
-        <v>-0.05046544299123846</v>
+        <v>0.04771564423167637</v>
       </c>
       <c r="AD12">
-        <v>2.89</v>
+        <v>61.5</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>2.89</v>
+        <v>61.5</v>
       </c>
       <c r="AG12">
-        <v>2.44</v>
+        <v>44.2</v>
       </c>
       <c r="AH12">
-        <v>0.06817645671148856</v>
+        <v>0.3360655737704918</v>
       </c>
       <c r="AI12">
-        <v>0.08306984765737281</v>
+        <v>0.1656788793103448</v>
       </c>
       <c r="AJ12">
-        <v>0.05817835002384359</v>
+        <v>0.2667471333735667</v>
       </c>
       <c r="AK12">
-        <v>0.07105416423995341</v>
+        <v>0.1248940378638033</v>
       </c>
       <c r="AL12">
-        <v>0.08699999999999999</v>
+        <v>33.6</v>
       </c>
       <c r="AM12">
-        <v>-0.429</v>
+        <v>33.158</v>
+      </c>
+      <c r="AN12">
+        <v>1.351648351648352</v>
       </c>
       <c r="AO12">
-        <v>-0.632183908045977</v>
+        <v>1.273809523809524</v>
+      </c>
+      <c r="AP12">
+        <v>0.9714285714285715</v>
       </c>
       <c r="AQ12">
-        <v>0.1282051282051282</v>
+        <v>1.290789553049038</v>
       </c>
     </row>
     <row r="13">
@@ -1957,7 +2002,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CNH Co., Ltd. (KOSDAQ:A023460)</t>
+          <t>FnGuide Inc. (KOSDAQ:A064850)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1965,110 +2010,116 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D13">
-        <v>0.483</v>
-      </c>
       <c r="G13">
-        <v>0</v>
+        <v>0.2775229357798165</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>0.2775229357798165</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>0.2174311926605505</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>0.2045613193681638</v>
       </c>
       <c r="K13">
-        <v>-3.01</v>
+        <v>5.62</v>
       </c>
       <c r="L13">
-        <v>-0.01646608315098468</v>
+        <v>0.2577981651376147</v>
       </c>
       <c r="M13">
-        <v>2.0076</v>
+        <v>3.7376</v>
       </c>
       <c r="N13">
-        <v>0.02712972972972973</v>
+        <v>0.06421993127147765</v>
       </c>
       <c r="O13">
-        <v>-0.6669767441860466</v>
+        <v>0.6650533807829181</v>
       </c>
       <c r="P13">
-        <v>0.4676</v>
+        <v>1.5276</v>
       </c>
       <c r="Q13">
-        <v>0.006318918918918919</v>
+        <v>0.02624742268041237</v>
       </c>
       <c r="R13">
-        <v>-0.1553488372093023</v>
+        <v>0.2718149466192171</v>
       </c>
       <c r="S13">
-        <v>1.54</v>
+        <v>2.21</v>
       </c>
       <c r="T13">
-        <v>0.7670850767085077</v>
+        <v>0.5912885273972602</v>
       </c>
       <c r="U13">
-        <v>5.42</v>
+        <v>7.48</v>
       </c>
       <c r="V13">
-        <v>0.07324324324324324</v>
+        <v>0.1285223367697594</v>
       </c>
       <c r="W13">
-        <v>-0.02675555555555555</v>
+        <v>0.1482849604221636</v>
       </c>
       <c r="X13">
-        <v>0.06464398664639279</v>
+        <v>0.05558692572167602</v>
       </c>
       <c r="Y13">
-        <v>-0.09139954220194835</v>
+        <v>0.09269803470048758</v>
       </c>
       <c r="Z13">
-        <v>0.7022396373554608</v>
+        <v>0.4636324968098682</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>0.0948412752493826</v>
       </c>
       <c r="AB13">
-        <v>0.05229996904215231</v>
+        <v>0.05030705608933792</v>
       </c>
       <c r="AC13">
-        <v>-0.05229996904215231</v>
+        <v>0.04453421916004468</v>
       </c>
       <c r="AD13">
-        <v>140.1</v>
+        <v>24.6</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>140.1</v>
+        <v>24.6</v>
       </c>
       <c r="AG13">
-        <v>134.68</v>
+        <v>17.12</v>
       </c>
       <c r="AH13">
-        <v>0.6543671181690799</v>
+        <v>0.2971014492753623</v>
       </c>
       <c r="AI13">
-        <v>0.6078091106290672</v>
+        <v>0.3649851632047478</v>
       </c>
       <c r="AJ13">
-        <v>0.6453900709219859</v>
+        <v>0.2272968667020712</v>
       </c>
       <c r="AK13">
-        <v>0.5983650257686156</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AM13">
-        <v>-1.04</v>
+        <v>0.4700000000000001</v>
+      </c>
+      <c r="AN13">
+        <v>4.190800681431005</v>
+      </c>
+      <c r="AO13">
+        <v>4.429906542056075</v>
+      </c>
+      <c r="AP13">
+        <v>2.916524701873935</v>
       </c>
       <c r="AQ13">
-        <v>-0</v>
+        <v>10.08510638297872</v>
       </c>
     </row>
     <row r="14">
@@ -2079,7 +2130,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Meritz Financial Group Inc. (KOSE:A138040)</t>
+          <t>SM Life Design Group Co., Ltd. (KOSDAQ:A063440)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2088,109 +2139,115 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.132</v>
-      </c>
-      <c r="E14">
-        <v>0.252</v>
+        <v>0.348</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>0.06784869976359338</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>0.0663624901497242</v>
       </c>
       <c r="K14">
-        <v>757.4</v>
+        <v>3.08</v>
       </c>
       <c r="L14">
-        <v>0.06347211048538483</v>
+        <v>0.07281323877068559</v>
       </c>
       <c r="M14">
-        <v>120.185</v>
+        <v>-0</v>
       </c>
       <c r="N14">
-        <v>0.02904071523498852</v>
+        <v>-0</v>
       </c>
       <c r="O14">
-        <v>0.1586810139952469</v>
+        <v>-0</v>
       </c>
       <c r="P14">
-        <v>17.885</v>
+        <v>-0</v>
       </c>
       <c r="Q14">
-        <v>0.004321614111393016</v>
+        <v>-0</v>
       </c>
       <c r="R14">
-        <v>0.02361367837338262</v>
+        <v>-0</v>
       </c>
       <c r="S14">
-        <v>102.3</v>
-      </c>
-      <c r="T14">
-        <v>0.8511877522153348</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>3858.9</v>
+        <v>4.72</v>
       </c>
       <c r="V14">
-        <v>0.9324392895976803</v>
+        <v>0.06810966810966811</v>
       </c>
       <c r="W14">
-        <v>0.2459729799948039</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="X14">
-        <v>0.1257424194563558</v>
+        <v>0.05180419670410219</v>
       </c>
       <c r="Y14">
-        <v>0.1202305605384481</v>
+        <v>0.0356958032958978</v>
       </c>
       <c r="Z14">
-        <v>0.2755314801088937</v>
+        <v>1.374269005847953</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>0.09119991336365606</v>
       </c>
       <c r="AB14">
-        <v>0.05338000646841085</v>
+        <v>0.05155117943746004</v>
       </c>
       <c r="AC14">
-        <v>-0.05338000646841085</v>
+        <v>0.03964873392619601</v>
       </c>
       <c r="AD14">
-        <v>39403.8</v>
+        <v>1.87</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>39403.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG14">
-        <v>35544.9</v>
+        <v>-2.85</v>
       </c>
       <c r="AH14">
-        <v>0.9049544925279556</v>
+        <v>0.02627511591962906</v>
       </c>
       <c r="AI14">
-        <v>0.9106683522421312</v>
+        <v>0.04351873400046544</v>
       </c>
       <c r="AJ14">
-        <v>0.8957120609625183</v>
+        <v>-0.04288939051918735</v>
       </c>
       <c r="AK14">
-        <v>0.9019213300110123</v>
+        <v>-0.07450980392156861</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>0.095</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>-0.479</v>
+      </c>
+      <c r="AN14">
+        <v>0.5297450424929179</v>
+      </c>
+      <c r="AO14">
+        <v>30.21052631578948</v>
+      </c>
+      <c r="AP14">
+        <v>-0.8073654390934843</v>
+      </c>
+      <c r="AQ14">
+        <v>-5.991649269311065</v>
       </c>
     </row>
     <row r="15">
@@ -2201,7 +2258,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mirae Asset Securities Co. Ltd. (KOSE:A006800)</t>
+          <t>KG Mobilians Co., Ltd (KOSDAQ:A046440)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2210,109 +2267,121 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.159</v>
+        <v>0.06150000000000001</v>
       </c>
       <c r="E15">
-        <v>0.198</v>
+        <v>0.0183</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>0.194971181556196</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>0.1911623439000961</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>0.1147934678194044</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>0.08139403503956817</v>
       </c>
       <c r="K15">
-        <v>505.6</v>
+        <v>16.1</v>
       </c>
       <c r="L15">
-        <v>0.04335485641276293</v>
+        <v>0.07732949087415947</v>
       </c>
       <c r="M15">
-        <v>255</v>
+        <v>6.047300000000001</v>
       </c>
       <c r="N15">
-        <v>0.0964374858180168</v>
+        <v>0.03841994917407878</v>
       </c>
       <c r="O15">
-        <v>0.5043512658227848</v>
+        <v>0.3756086956521739</v>
       </c>
       <c r="P15">
-        <v>132</v>
+        <v>6.047300000000001</v>
       </c>
       <c r="Q15">
-        <v>0.04992058089403222</v>
+        <v>0.03841994917407878</v>
       </c>
       <c r="R15">
-        <v>0.2610759493670886</v>
+        <v>0.3756086956521739</v>
       </c>
       <c r="S15">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>0.4823529411764706</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>2497.2</v>
+        <v>9.51</v>
       </c>
       <c r="V15">
-        <v>0.944406625822555</v>
+        <v>0.06041931385006353</v>
       </c>
       <c r="W15">
-        <v>0.05694270815735829</v>
+        <v>0.07562235791451385</v>
       </c>
       <c r="X15">
-        <v>0.1944289119377287</v>
+        <v>0.05451617518109218</v>
       </c>
       <c r="Y15">
-        <v>-0.1374862037803704</v>
+        <v>0.02110618273342167</v>
       </c>
       <c r="Z15">
-        <v>0.2200084517777031</v>
+        <v>1.04047976011994</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>0.08468884605316389</v>
       </c>
       <c r="AB15">
-        <v>0.05626471901266216</v>
+        <v>0.05159082264049568</v>
       </c>
       <c r="AC15">
-        <v>-0.05626471901266216</v>
+        <v>0.03309802341266821</v>
       </c>
       <c r="AD15">
-        <v>47851.2</v>
+        <v>48.9</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>47851.2</v>
+        <v>48.9</v>
       </c>
       <c r="AG15">
-        <v>45354</v>
+        <v>39.39</v>
       </c>
       <c r="AH15">
-        <v>0.947634834064093</v>
+        <v>0.2370334464372273</v>
       </c>
       <c r="AI15">
-        <v>0.8620999037931445</v>
+        <v>0.1674084217733653</v>
       </c>
       <c r="AJ15">
-        <v>0.9449104341412804</v>
+        <v>0.2001626098887138</v>
       </c>
       <c r="AK15">
-        <v>0.8556034726702662</v>
+        <v>0.1393892211330904</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>-0.76</v>
+      </c>
+      <c r="AN15">
+        <v>1.608552631578947</v>
+      </c>
+      <c r="AO15">
+        <v>19.75206611570248</v>
+      </c>
+      <c r="AP15">
+        <v>1.295723684210526</v>
+      </c>
+      <c r="AQ15">
+        <v>-31.44736842105263</v>
       </c>
     </row>
     <row r="16">
@@ -2323,7 +2392,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IBKS No.15 Special Purpose Acquisition Company (KOSDAQ:A373200)</t>
+          <t>NICE Holdings Co., Ltd. (KOSE:A034310)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2331,71 +2400,1544 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D16">
+        <v>0.125</v>
+      </c>
+      <c r="E16">
+        <v>-0.07870000000000001</v>
+      </c>
+      <c r="G16">
+        <v>0.1370634804992958</v>
+      </c>
+      <c r="H16">
+        <v>0.1263295934722425</v>
+      </c>
+      <c r="I16">
+        <v>0.02836466074117247</v>
+      </c>
+      <c r="J16">
+        <v>0.01844650542633043</v>
+      </c>
       <c r="K16">
-        <v>-0.053</v>
+        <v>22.6</v>
+      </c>
+      <c r="L16">
+        <v>0.01097673514983729</v>
       </c>
       <c r="M16">
+        <v>39.319</v>
+      </c>
+      <c r="N16">
+        <v>0.1073702894593118</v>
+      </c>
+      <c r="O16">
+        <v>1.739778761061947</v>
+      </c>
+      <c r="P16">
+        <v>10.919</v>
+      </c>
+      <c r="Q16">
+        <v>0.02981703986892408</v>
+      </c>
+      <c r="R16">
+        <v>0.4831415929203539</v>
+      </c>
+      <c r="S16">
+        <v>28.4</v>
+      </c>
+      <c r="T16">
+        <v>0.7222971082682673</v>
+      </c>
+      <c r="U16">
+        <v>496.3</v>
+      </c>
+      <c r="V16">
+        <v>1.355270344074276</v>
+      </c>
+      <c r="W16">
+        <v>0.04362092260181432</v>
+      </c>
+      <c r="X16">
+        <v>0.07149312368207555</v>
+      </c>
+      <c r="Y16">
+        <v>-0.02787220108026123</v>
+      </c>
+      <c r="Z16">
+        <v>2.445249406175773</v>
+      </c>
+      <c r="AA16">
+        <v>0.04510630643975263</v>
+      </c>
+      <c r="AB16">
+        <v>0.04872664386556259</v>
+      </c>
+      <c r="AC16">
+        <v>-0.003620337425809958</v>
+      </c>
+      <c r="AD16">
+        <v>764.1</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>764.1</v>
+      </c>
+      <c r="AG16">
+        <v>267.8</v>
+      </c>
+      <c r="AH16">
+        <v>0.6760152171989737</v>
+      </c>
+      <c r="AI16">
+        <v>0.4255639097744361</v>
+      </c>
+      <c r="AJ16">
+        <v>0.422397476340694</v>
+      </c>
+      <c r="AK16">
+        <v>0.2061268472906404</v>
+      </c>
+      <c r="AL16">
+        <v>39</v>
+      </c>
+      <c r="AM16">
+        <v>21.8</v>
+      </c>
+      <c r="AN16">
+        <v>3.892511462047886</v>
+      </c>
+      <c r="AO16">
+        <v>1.497435897435897</v>
+      </c>
+      <c r="AP16">
+        <v>1.364238410596027</v>
+      </c>
+      <c r="AQ16">
+        <v>2.678899082568807</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GalaxiaMoneytree Co.,Ltd (KOSDAQ:A094480)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>0.106</v>
+      </c>
+      <c r="E17">
+        <v>-0.263</v>
+      </c>
+      <c r="G17">
+        <v>0.08780231335436382</v>
+      </c>
+      <c r="H17">
+        <v>0.08780231335436382</v>
+      </c>
+      <c r="I17">
+        <v>0.05425867507886436</v>
+      </c>
+      <c r="J17">
+        <v>0.02712933753943218</v>
+      </c>
+      <c r="K17">
+        <v>0.533</v>
+      </c>
+      <c r="L17">
+        <v>0.005604626708727656</v>
+      </c>
+      <c r="M17">
+        <v>1.2936</v>
+      </c>
+      <c r="N17">
+        <v>0.003706590257879656</v>
+      </c>
+      <c r="O17">
+        <v>2.427016885553471</v>
+      </c>
+      <c r="P17">
+        <v>1.2936</v>
+      </c>
+      <c r="Q17">
+        <v>0.003706590257879656</v>
+      </c>
+      <c r="R17">
+        <v>2.427016885553471</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>12.4</v>
+      </c>
+      <c r="V17">
+        <v>0.03553008595988539</v>
+      </c>
+      <c r="W17">
+        <v>0.006645885286783042</v>
+      </c>
+      <c r="X17">
+        <v>0.05313769067726376</v>
+      </c>
+      <c r="Y17">
+        <v>-0.04649180539048071</v>
+      </c>
+      <c r="Z17">
+        <v>0.8509305654974947</v>
+      </c>
+      <c r="AA17">
+        <v>0.02308518253400143</v>
+      </c>
+      <c r="AB17">
+        <v>0.05185876518021048</v>
+      </c>
+      <c r="AC17">
+        <v>-0.02877358264620905</v>
+      </c>
+      <c r="AD17">
+        <v>58.1</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>58.1</v>
+      </c>
+      <c r="AG17">
+        <v>45.7</v>
+      </c>
+      <c r="AH17">
+        <v>0.142716777204618</v>
+      </c>
+      <c r="AI17">
+        <v>0.4048780487804878</v>
+      </c>
+      <c r="AJ17">
+        <v>0.115784139853053</v>
+      </c>
+      <c r="AK17">
+        <v>0.3485888634630053</v>
+      </c>
+      <c r="AL17">
+        <v>4.11</v>
+      </c>
+      <c r="AM17">
+        <v>4.027</v>
+      </c>
+      <c r="AN17">
+        <v>8.993808049535604</v>
+      </c>
+      <c r="AO17">
+        <v>1.255474452554745</v>
+      </c>
+      <c r="AP17">
+        <v>7.074303405572756</v>
+      </c>
+      <c r="AQ17">
+        <v>1.281350881549541</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Danal Co., Ltd. (KOSDAQ:A064260)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>0.0956</v>
+      </c>
+      <c r="G18">
+        <v>0.04763181411974977</v>
+      </c>
+      <c r="H18">
+        <v>0.02712243074173369</v>
+      </c>
+      <c r="I18">
+        <v>0.02613941018766756</v>
+      </c>
+      <c r="J18">
+        <v>0.02613941018766756</v>
+      </c>
+      <c r="K18">
+        <v>-7.88</v>
+      </c>
+      <c r="L18">
+        <v>-0.03521000893655049</v>
+      </c>
+      <c r="M18">
         <v>-0</v>
       </c>
-      <c r="N16">
+      <c r="N18">
         <v>-0</v>
       </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
         <v>-0</v>
       </c>
-      <c r="Q16">
+      <c r="Q18">
         <v>-0</v>
       </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>0.04947963150541988</v>
-      </c>
-      <c r="AB16">
-        <v>0.04947963150541988</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>0</v>
-      </c>
-      <c r="AH16">
-        <v>0</v>
-      </c>
-      <c r="AI16">
-        <v>0</v>
-      </c>
-      <c r="AJ16">
-        <v>0</v>
-      </c>
-      <c r="AK16">
-        <v>0</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>27.9</v>
+      </c>
+      <c r="V18">
+        <v>0.1152416356877323</v>
+      </c>
+      <c r="W18">
+        <v>-0.03502222222222222</v>
+      </c>
+      <c r="X18">
+        <v>0.05898154214288905</v>
+      </c>
+      <c r="Y18">
+        <v>-0.09400376436511126</v>
+      </c>
+      <c r="Z18">
+        <v>0.6453845488364046</v>
+      </c>
+      <c r="AA18">
+        <v>0.01686997145081754</v>
+      </c>
+      <c r="AB18">
+        <v>0.05162852998172025</v>
+      </c>
+      <c r="AC18">
+        <v>-0.03475855853090271</v>
+      </c>
+      <c r="AD18">
+        <v>188.3</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>188.3</v>
+      </c>
+      <c r="AG18">
+        <v>160.4</v>
+      </c>
+      <c r="AH18">
+        <v>0.4375000000000001</v>
+      </c>
+      <c r="AI18">
+        <v>0.44046783625731</v>
+      </c>
+      <c r="AJ18">
+        <v>0.3985093167701864</v>
+      </c>
+      <c r="AK18">
+        <v>0.4014014014014014</v>
+      </c>
+      <c r="AL18">
+        <v>7.34</v>
+      </c>
+      <c r="AM18">
+        <v>5.26</v>
+      </c>
+      <c r="AN18">
+        <v>13.45</v>
+      </c>
+      <c r="AO18">
+        <v>0.7970027247956403</v>
+      </c>
+      <c r="AP18">
+        <v>11.45714285714286</v>
+      </c>
+      <c r="AQ18">
+        <v>1.112167300380228</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Han Kook Capital.Co., Ltd (KOSDAQ:A023760)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>0.206</v>
+      </c>
+      <c r="E19">
+        <v>0.344</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>41.9</v>
+      </c>
+      <c r="L19">
+        <v>0.4262461851475076</v>
+      </c>
+      <c r="M19">
+        <v>6.564600000000001</v>
+      </c>
+      <c r="N19">
+        <v>0.0460350631136045</v>
+      </c>
+      <c r="O19">
+        <v>0.156673031026253</v>
+      </c>
+      <c r="P19">
+        <v>6.564600000000001</v>
+      </c>
+      <c r="Q19">
+        <v>0.0460350631136045</v>
+      </c>
+      <c r="R19">
+        <v>0.156673031026253</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>324.8</v>
+      </c>
+      <c r="V19">
+        <v>2.277699859747546</v>
+      </c>
+      <c r="W19">
+        <v>0.1335671023270641</v>
+      </c>
+      <c r="X19">
+        <v>0.2092876256273984</v>
+      </c>
+      <c r="Y19">
+        <v>-0.0757205233003343</v>
+      </c>
+      <c r="Z19">
+        <v>0.04636792452830189</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0.047613662771799</v>
+      </c>
+      <c r="AC19">
+        <v>-0.047613662771799</v>
+      </c>
+      <c r="AD19">
+        <v>2353</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>2353</v>
+      </c>
+      <c r="AG19">
+        <v>2028.2</v>
+      </c>
+      <c r="AH19">
+        <v>0.9428594326013785</v>
+      </c>
+      <c r="AI19">
+        <v>0.8638032305433186</v>
+      </c>
+      <c r="AJ19">
+        <v>0.9343099318223695</v>
+      </c>
+      <c r="AK19">
+        <v>0.8453651217072359</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Samsung Card Co., Ltd. (KOSE:A029780)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="E20">
+        <v>0.108</v>
+      </c>
+      <c r="K20">
+        <v>442.6</v>
+      </c>
+      <c r="M20">
+        <v>198.462</v>
+      </c>
+      <c r="N20">
+        <v>0.07398948663460463</v>
+      </c>
+      <c r="O20">
+        <v>0.4484003615002259</v>
+      </c>
+      <c r="P20">
+        <v>198.462</v>
+      </c>
+      <c r="Q20">
+        <v>0.07398948663460463</v>
+      </c>
+      <c r="R20">
+        <v>0.4484003615002259</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>1466.4</v>
+      </c>
+      <c r="V20">
+        <v>0.5466950005592216</v>
+      </c>
+      <c r="W20">
+        <v>0.08143813939795393</v>
+      </c>
+      <c r="X20">
+        <v>0.09811291309778178</v>
+      </c>
+      <c r="Y20">
+        <v>-0.01667477369982785</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0.04808574073556552</v>
+      </c>
+      <c r="AC20">
+        <v>-0.04808574073556552</v>
+      </c>
+      <c r="AD20">
+        <v>13065.9</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>13065.9</v>
+      </c>
+      <c r="AG20">
+        <v>11599.5</v>
+      </c>
+      <c r="AH20">
+        <v>0.8296757724692345</v>
+      </c>
+      <c r="AI20">
+        <v>0.6865479499561249</v>
+      </c>
+      <c r="AJ20">
+        <v>0.8121875393857918</v>
+      </c>
+      <c r="AK20">
+        <v>0.6603795068574259</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CNH Co., Ltd. (KOSDAQ:A023460)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>0.209</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>-15.8</v>
+      </c>
+      <c r="L21">
+        <v>-0.1370338248048569</v>
+      </c>
+      <c r="M21">
+        <v>2.055</v>
+      </c>
+      <c r="N21">
+        <v>0.04185336048879838</v>
+      </c>
+      <c r="O21">
+        <v>-0.1300632911392405</v>
+      </c>
+      <c r="P21">
+        <v>0.495</v>
+      </c>
+      <c r="Q21">
+        <v>0.01008146639511202</v>
+      </c>
+      <c r="R21">
+        <v>-0.03132911392405063</v>
+      </c>
+      <c r="S21">
+        <v>1.56</v>
+      </c>
+      <c r="T21">
+        <v>0.7591240875912408</v>
+      </c>
+      <c r="U21">
+        <v>4.34</v>
+      </c>
+      <c r="V21">
+        <v>0.08839103869653767</v>
+      </c>
+      <c r="W21">
+        <v>-0.1732456140350877</v>
+      </c>
+      <c r="X21">
+        <v>0.08230854063434286</v>
+      </c>
+      <c r="Y21">
+        <v>-0.2555541546694306</v>
+      </c>
+      <c r="Z21">
+        <v>0.5137917205115636</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0.04836418726814112</v>
+      </c>
+      <c r="AC21">
+        <v>-0.04836418726814112</v>
+      </c>
+      <c r="AD21">
+        <v>158</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>158</v>
+      </c>
+      <c r="AG21">
+        <v>153.66</v>
+      </c>
+      <c r="AH21">
+        <v>0.7629164654756156</v>
+      </c>
+      <c r="AI21">
+        <v>0.6675116180819604</v>
+      </c>
+      <c r="AJ21">
+        <v>0.7578417833892287</v>
+      </c>
+      <c r="AK21">
+        <v>0.6613014288173523</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>-0.911</v>
+      </c>
+      <c r="AQ21">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Mason Capital Corporation (KOSDAQ:A021880)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>-0.262</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>-2.2</v>
+      </c>
+      <c r="L22">
+        <v>-0.9016393442622952</v>
+      </c>
+      <c r="M22">
+        <v>-0</v>
+      </c>
+      <c r="N22">
+        <v>-0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>-0</v>
+      </c>
+      <c r="Q22">
+        <v>-0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>4.67</v>
+      </c>
+      <c r="V22">
+        <v>0.09247524752475247</v>
+      </c>
+      <c r="W22">
+        <v>-0.05655526992287918</v>
+      </c>
+      <c r="X22">
+        <v>0.0528126578332612</v>
+      </c>
+      <c r="Y22">
+        <v>-0.1093679277561404</v>
+      </c>
+      <c r="Z22">
+        <v>0.06842400448681997</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0.05156824055373771</v>
+      </c>
+      <c r="AC22">
+        <v>-0.05156824055373771</v>
+      </c>
+      <c r="AD22">
+        <v>6.69</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>6.69</v>
+      </c>
+      <c r="AG22">
+        <v>2.02</v>
+      </c>
+      <c r="AH22">
+        <v>0.1169784927434866</v>
+      </c>
+      <c r="AI22">
+        <v>0.125775521714608</v>
+      </c>
+      <c r="AJ22">
+        <v>0.03846153846153847</v>
+      </c>
+      <c r="AK22">
+        <v>0.0416323165704864</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Meritz Financial Group Inc. (KOSE:A138040)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>0.111</v>
+      </c>
+      <c r="E23">
+        <v>0.386</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>1219.6</v>
+      </c>
+      <c r="L23">
+        <v>0.09396862575892995</v>
+      </c>
+      <c r="M23">
+        <v>217.52</v>
+      </c>
+      <c r="N23">
+        <v>0.02492523118174839</v>
+      </c>
+      <c r="O23">
+        <v>0.1783535585437848</v>
+      </c>
+      <c r="P23">
+        <v>14.82</v>
+      </c>
+      <c r="Q23">
+        <v>0.001698197527186057</v>
+      </c>
+      <c r="R23">
+        <v>0.01215152509019351</v>
+      </c>
+      <c r="S23">
+        <v>202.7</v>
+      </c>
+      <c r="T23">
+        <v>0.9318683339463039</v>
+      </c>
+      <c r="U23">
+        <v>3627.2</v>
+      </c>
+      <c r="V23">
+        <v>0.4156344177199234</v>
+      </c>
+      <c r="W23">
+        <v>0.580789561407686</v>
+      </c>
+      <c r="X23">
+        <v>0.09236544486780077</v>
+      </c>
+      <c r="Y23">
+        <v>0.4884241165398853</v>
+      </c>
+      <c r="Z23">
+        <v>0.3447700612036722</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0.05169864241886623</v>
+      </c>
+      <c r="AC23">
+        <v>-0.05169864241886623</v>
+      </c>
+      <c r="AD23">
+        <v>37263.3</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>37263.3</v>
+      </c>
+      <c r="AG23">
+        <v>33636.10000000001</v>
+      </c>
+      <c r="AH23">
+        <v>0.8102443564063648</v>
+      </c>
+      <c r="AI23">
+        <v>0.8390273008725022</v>
+      </c>
+      <c r="AJ23">
+        <v>0.7939971201284139</v>
+      </c>
+      <c r="AK23">
+        <v>0.8247113543359986</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NH Special Purpose Acquisition 20 Company (KOSDAQ:A391060)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="K24">
+        <v>0.983</v>
+      </c>
+      <c r="M24">
+        <v>0.054</v>
+      </c>
+      <c r="N24">
+        <v>0.001402597402597403</v>
+      </c>
+      <c r="O24">
+        <v>0.05493387589013225</v>
+      </c>
+      <c r="P24">
+        <v>-0</v>
+      </c>
+      <c r="Q24">
+        <v>-0</v>
+      </c>
+      <c r="R24">
+        <v>-0</v>
+      </c>
+      <c r="S24">
+        <v>0.054</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+      <c r="U24">
+        <v>0.292</v>
+      </c>
+      <c r="V24">
+        <v>0.007584415584415584</v>
+      </c>
+      <c r="W24">
+        <v>0.03081504702194357</v>
+      </c>
+      <c r="X24">
+        <v>0.05232839260391749</v>
+      </c>
+      <c r="Y24">
+        <v>-0.02151334558197391</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>-0.001269608638780947</v>
+      </c>
+      <c r="AB24">
+        <v>0.05123079076687895</v>
+      </c>
+      <c r="AC24">
+        <v>-0.0525003994056599</v>
+      </c>
+      <c r="AD24">
+        <v>3.15</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>3.15</v>
+      </c>
+      <c r="AG24">
+        <v>2.858</v>
+      </c>
+      <c r="AH24">
+        <v>0.07563025210084033</v>
+      </c>
+      <c r="AI24">
+        <v>0.08278580814717477</v>
+      </c>
+      <c r="AJ24">
+        <v>0.06910392185308768</v>
+      </c>
+      <c r="AK24">
+        <v>0.07569256846231263</v>
+      </c>
+      <c r="AL24">
+        <v>0.068</v>
+      </c>
+      <c r="AM24">
+        <v>-1.272</v>
+      </c>
+      <c r="AO24">
+        <v>-0.7941176470588235</v>
+      </c>
+      <c r="AQ24">
+        <v>0.04245283018867924</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Mirae Asset Securities Co., Ltd. (KOSE:A006800)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>0.0312</v>
+      </c>
+      <c r="E25">
+        <v>-0.00185</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>386.9</v>
+      </c>
+      <c r="L25">
+        <v>0.04414449363333486</v>
+      </c>
+      <c r="M25">
+        <v>95.67</v>
+      </c>
+      <c r="N25">
+        <v>0.03012848774957486</v>
+      </c>
+      <c r="O25">
+        <v>0.247273197208581</v>
+      </c>
+      <c r="P25">
+        <v>91.7</v>
+      </c>
+      <c r="Q25">
+        <v>0.02887825155885873</v>
+      </c>
+      <c r="R25">
+        <v>0.2370121478418196</v>
+      </c>
+      <c r="S25">
+        <v>3.969999999999999</v>
+      </c>
+      <c r="T25">
+        <v>0.0414968119577715</v>
+      </c>
+      <c r="U25">
+        <v>1946.1</v>
+      </c>
+      <c r="V25">
+        <v>0.6128676702147761</v>
+      </c>
+      <c r="W25">
+        <v>0.05109614368726888</v>
+      </c>
+      <c r="X25">
+        <v>0.2288410209777476</v>
+      </c>
+      <c r="Y25">
+        <v>-0.1777448772904787</v>
+      </c>
+      <c r="Z25">
+        <v>0.1664684989268552</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0.05362405005471806</v>
+      </c>
+      <c r="AC25">
+        <v>-0.05362405005471806</v>
+      </c>
+      <c r="AD25">
+        <v>58891.3</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>58891.3</v>
+      </c>
+      <c r="AG25">
+        <v>56945.2</v>
+      </c>
+      <c r="AH25">
+        <v>0.9488389103980073</v>
+      </c>
+      <c r="AI25">
+        <v>0.8733771915514597</v>
+      </c>
+      <c r="AJ25">
+        <v>0.9471828291800148</v>
+      </c>
+      <c r="AK25">
+        <v>0.8696140848124637</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SCI Information Service Inc. (KOSDAQ:A036120)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>-0.06849999999999999</v>
+      </c>
+      <c r="E26">
+        <v>-0.282</v>
+      </c>
+      <c r="G26">
+        <v>0.2073929961089494</v>
+      </c>
+      <c r="H26">
+        <v>0.2073929961089494</v>
+      </c>
+      <c r="I26">
+        <v>-0.007198443579766537</v>
+      </c>
+      <c r="J26">
+        <v>-0.007198443579766537</v>
+      </c>
+      <c r="K26">
+        <v>-0.32</v>
+      </c>
+      <c r="L26">
+        <v>-0.01245136186770428</v>
+      </c>
+      <c r="M26">
+        <v>1.2802</v>
+      </c>
+      <c r="N26">
+        <v>0.01360467587672689</v>
+      </c>
+      <c r="O26">
+        <v>-4.000625</v>
+      </c>
+      <c r="P26">
+        <v>1.2802</v>
+      </c>
+      <c r="Q26">
+        <v>0.01360467587672689</v>
+      </c>
+      <c r="R26">
+        <v>-4.000625</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>2.95</v>
+      </c>
+      <c r="V26">
+        <v>0.03134962805526036</v>
+      </c>
+      <c r="W26">
+        <v>-0.01454545454545455</v>
+      </c>
+      <c r="X26">
+        <v>0.05160475334315065</v>
+      </c>
+      <c r="Y26">
+        <v>-0.06615020788860519</v>
+      </c>
+      <c r="Z26">
+        <v>1.714933938342453</v>
+      </c>
+      <c r="AA26">
+        <v>-0.01234485519818497</v>
+      </c>
+      <c r="AB26">
+        <v>0.0515595599744333</v>
+      </c>
+      <c r="AC26">
+        <v>-0.06390441517261827</v>
+      </c>
+      <c r="AD26">
+        <v>0.576</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0.576</v>
+      </c>
+      <c r="AG26">
+        <v>-2.374</v>
+      </c>
+      <c r="AH26">
+        <v>0.006083907220414889</v>
+      </c>
+      <c r="AI26">
+        <v>0.02528977871443625</v>
+      </c>
+      <c r="AJ26">
+        <v>-0.02588142947473999</v>
+      </c>
+      <c r="AK26">
+        <v>-0.1197417532533037</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+      <c r="AN26">
+        <v>0.3764705882352941</v>
+      </c>
+      <c r="AP26">
+        <v>-1.551633986928105</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kakao Pay Corp. (KOSE:A377300)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="F27">
+        <v>0.344</v>
+      </c>
+      <c r="G27">
+        <v>-0.01185882352941177</v>
+      </c>
+      <c r="H27">
+        <v>-0.01185882352941177</v>
+      </c>
+      <c r="I27">
+        <v>-0.1002352941176471</v>
+      </c>
+      <c r="J27">
+        <v>-0.1002352941176471</v>
+      </c>
+      <c r="K27">
+        <v>33.3</v>
+      </c>
+      <c r="L27">
+        <v>0.07835294117647058</v>
+      </c>
+      <c r="M27">
+        <v>-0</v>
+      </c>
+      <c r="N27">
+        <v>-0</v>
+      </c>
+      <c r="O27">
+        <v>-0</v>
+      </c>
+      <c r="P27">
+        <v>-0</v>
+      </c>
+      <c r="Q27">
+        <v>-0</v>
+      </c>
+      <c r="R27">
+        <v>-0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>840</v>
+      </c>
+      <c r="V27">
+        <v>0.163322445170322</v>
+      </c>
+      <c r="W27">
+        <v>0.0279432743140052</v>
+      </c>
+      <c r="X27">
+        <v>0.05168303763484471</v>
+      </c>
+      <c r="Y27">
+        <v>-0.02373976332083951</v>
+      </c>
+      <c r="Z27">
+        <v>1.508161816891412</v>
+      </c>
+      <c r="AA27">
+        <v>-0.1511710432931156</v>
+      </c>
+      <c r="AB27">
+        <v>0.0515488908782548</v>
+      </c>
+      <c r="AC27">
+        <v>-0.2027199341713704</v>
+      </c>
+      <c r="AD27">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AG27">
+        <v>-766.4</v>
+      </c>
+      <c r="AH27">
+        <v>0.01410826560343505</v>
+      </c>
+      <c r="AI27">
+        <v>0.04856483008907951</v>
+      </c>
+      <c r="AJ27">
+        <v>-0.1751050996161579</v>
+      </c>
+      <c r="AK27">
+        <v>-1.134566987416728</v>
+      </c>
+      <c r="AL27">
+        <v>4.68</v>
+      </c>
+      <c r="AM27">
+        <v>-23.02</v>
+      </c>
+      <c r="AN27">
+        <v>-8.232662192393736</v>
+      </c>
+      <c r="AO27">
+        <v>-9.102564102564104</v>
+      </c>
+      <c r="AP27">
+        <v>85.72706935123043</v>
+      </c>
+      <c r="AQ27">
+        <v>1.850564726324935</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Yuanta 11 Special Purpose Acquisition Company (KOSDAQ:A444920)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="K28">
+        <v>-0.062</v>
+      </c>
+      <c r="M28">
+        <v>-0</v>
+      </c>
+      <c r="N28">
+        <v>-0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>-0</v>
+      </c>
+      <c r="Q28">
+        <v>-0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0.28</v>
+      </c>
+      <c r="V28">
+        <v>0.03431372549019608</v>
+      </c>
+      <c r="X28">
+        <v>0.0527880580409885</v>
+      </c>
+      <c r="AB28">
+        <v>0.05179799840018712</v>
+      </c>
+      <c r="AD28">
+        <v>1.06</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>1.06</v>
+      </c>
+      <c r="AG28">
+        <v>0.78</v>
+      </c>
+      <c r="AH28">
+        <v>0.1149674620390456</v>
+      </c>
+      <c r="AI28">
+        <v>0.1211428571428571</v>
+      </c>
+      <c r="AJ28">
+        <v>0.08724832214765102</v>
+      </c>
+      <c r="AK28">
+        <v>0.09208972845336481</v>
+      </c>
+      <c r="AL28">
+        <v>0.046</v>
+      </c>
+      <c r="AM28">
+        <v>0.045</v>
+      </c>
+      <c r="AO28">
+        <v>-0.7173913043478262</v>
+      </c>
+      <c r="AQ28">
+        <v>-0.7333333333333334</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/south_korea/south_korea_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,109 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0278</v>
+        <v>0.08745</v>
       </c>
       <c r="E2">
-        <v>-0.00557</v>
+        <v>0.0465</v>
+      </c>
+      <c r="F2">
+        <v>1.963</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.0201616343064074</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0190228943168562</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.01057296624179662</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.008250086199171364</v>
       </c>
       <c r="K2">
-        <v>407.3</v>
+        <v>2894.516</v>
       </c>
       <c r="L2">
-        <v>0.03775456289800799</v>
+        <v>0.1035760650974386</v>
       </c>
       <c r="M2">
-        <v>222.9</v>
+        <v>1410.76322</v>
       </c>
       <c r="N2">
-        <v>0.08043737144094404</v>
+        <v>0.06209011752009795</v>
       </c>
       <c r="O2">
-        <v>0.5472624601031181</v>
+        <v>0.4873917504688176</v>
       </c>
       <c r="P2">
-        <v>68.40000000000001</v>
+        <v>663.39422</v>
       </c>
       <c r="Q2">
-        <v>0.02468333874634622</v>
+        <v>0.02919712145738653</v>
       </c>
       <c r="R2">
-        <v>0.1679351829118586</v>
+        <v>0.2291900338433092</v>
       </c>
       <c r="S2">
-        <v>154.5</v>
+        <v>747.369</v>
       </c>
       <c r="T2">
-        <v>0.693135935397039</v>
+        <v>0.5297621807860854</v>
       </c>
       <c r="U2">
-        <v>1421.3</v>
+        <v>8197.136</v>
       </c>
       <c r="V2">
-        <v>0.5129010140377468</v>
+        <v>0.36077006428352</v>
       </c>
       <c r="W2">
-        <v>0.04836200857288735</v>
+        <v>0.06527689469740258</v>
       </c>
       <c r="X2">
-        <v>0.2728832009162179</v>
+        <v>0.06051531270835077</v>
       </c>
       <c r="Y2">
-        <v>-0.2245211923433306</v>
+        <v>0.004761581989051814</v>
       </c>
       <c r="Z2">
-        <v>0.1658365691763281</v>
+        <v>0.2170295633098778</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.02883324620235495</v>
       </c>
       <c r="AB2">
-        <v>0.05605387102388523</v>
+        <v>0.05703720792119192</v>
       </c>
       <c r="AC2">
-        <v>-0.05605387102388523</v>
+        <v>-0.02689176394301755</v>
       </c>
       <c r="AD2">
-        <v>66487.39999999999</v>
+        <v>129947.467</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>66487.39999999999</v>
+        <v>129947.467</v>
       </c>
       <c r="AG2">
-        <v>65066.09999999999</v>
+        <v>121750.331</v>
       </c>
       <c r="AH2">
-        <v>0.9599890266176714</v>
+        <v>0.8511730175553288</v>
       </c>
       <c r="AI2">
-        <v>0.8840092964877571</v>
+        <v>0.8201982466956617</v>
       </c>
       <c r="AJ2">
-        <v>0.9591507314570765</v>
+        <v>0.8427287597957608</v>
       </c>
       <c r="AK2">
-        <v>0.8817751480893726</v>
+        <v>0.8103880226480172</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>110.028</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>15.96300000000001</v>
+      </c>
+      <c r="AN2">
+        <v>228.3024420667967</v>
+      </c>
+      <c r="AO2">
+        <v>2.685407350856146</v>
+      </c>
+      <c r="AP2">
+        <v>213.9010365607266</v>
+      </c>
+      <c r="AQ2">
+        <v>18.50967863183611</v>
       </c>
     </row>
     <row r="3">
@@ -701,118 +716,2493 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Korea Ratings Co., Ltd. (KOSDAQ:A034950)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.0208</v>
+      </c>
+      <c r="E3">
+        <v>0.0451</v>
+      </c>
+      <c r="G3">
+        <v>0.3125614489003881</v>
+      </c>
+      <c r="H3">
+        <v>0.3117723156532989</v>
+      </c>
+      <c r="I3">
+        <v>0.3104786545924968</v>
+      </c>
+      <c r="J3">
+        <v>0.254313414829135</v>
+      </c>
+      <c r="K3">
+        <v>18.4</v>
+      </c>
+      <c r="L3">
+        <v>0.2380336351875808</v>
+      </c>
+      <c r="M3">
+        <v>17.4386</v>
+      </c>
+      <c r="N3">
+        <v>0.06608033345964381</v>
+      </c>
+      <c r="O3">
+        <v>0.9477500000000001</v>
+      </c>
+      <c r="P3">
+        <v>17.4386</v>
+      </c>
+      <c r="Q3">
+        <v>0.06608033345964381</v>
+      </c>
+      <c r="R3">
+        <v>0.9477500000000001</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="V3">
+        <v>0.310344827586207</v>
+      </c>
+      <c r="W3">
+        <v>0.2530949105914718</v>
+      </c>
+      <c r="X3">
+        <v>0.05780103525786406</v>
+      </c>
+      <c r="Y3">
+        <v>0.1952938753336077</v>
+      </c>
+      <c r="Z3">
+        <v>25.5875537901357</v>
+      </c>
+      <c r="AA3">
+        <v>5</v>
+      </c>
+      <c r="AB3">
+        <v>0.0577129330041684</v>
+      </c>
+      <c r="AC3">
+        <v>4.942287066995831</v>
+      </c>
+      <c r="AD3">
+        <v>1.53</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>1.53</v>
+      </c>
+      <c r="AG3">
+        <v>-80.37</v>
+      </c>
+      <c r="AH3">
+        <v>0.00576423162415703</v>
+      </c>
+      <c r="AI3">
+        <v>0.01575208483475754</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.4379120579741733</v>
+      </c>
+      <c r="AK3">
+        <v>-5.277084701247541</v>
+      </c>
+      <c r="AL3">
+        <v>0.079</v>
+      </c>
+      <c r="AM3">
+        <v>-2.601</v>
+      </c>
+      <c r="AN3">
+        <v>0.05604395604395605</v>
+      </c>
+      <c r="AO3">
+        <v>303.7974683544304</v>
+      </c>
+      <c r="AP3">
+        <v>-2.943956043956044</v>
+      </c>
+      <c r="AQ3">
+        <v>-9.22722029988466</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Nice Information &amp; Telecommunication, Inc. (KOSDAQ:A036800)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.17</v>
+      </c>
+      <c r="E4">
+        <v>0.00453</v>
+      </c>
+      <c r="G4">
+        <v>0.06730506155950752</v>
+      </c>
+      <c r="H4">
+        <v>0.06730506155950752</v>
+      </c>
+      <c r="I4">
+        <v>0.03857729138166895</v>
+      </c>
+      <c r="J4">
+        <v>0.02980857153142775</v>
+      </c>
+      <c r="K4">
+        <v>23.3</v>
+      </c>
+      <c r="L4">
+        <v>0.03187414500683994</v>
+      </c>
+      <c r="M4">
+        <v>9.436119999999999</v>
+      </c>
+      <c r="N4">
+        <v>0.08860206572769952</v>
+      </c>
+      <c r="O4">
+        <v>0.4049836909871244</v>
+      </c>
+      <c r="P4">
+        <v>4.87612</v>
+      </c>
+      <c r="Q4">
+        <v>0.04578516431924883</v>
+      </c>
+      <c r="R4">
+        <v>0.2092755364806867</v>
+      </c>
+      <c r="S4">
+        <v>4.559999999999999</v>
+      </c>
+      <c r="T4">
+        <v>0.4832494711809514</v>
+      </c>
+      <c r="U4">
+        <v>188.1</v>
+      </c>
+      <c r="V4">
+        <v>1.766197183098591</v>
+      </c>
+      <c r="W4">
+        <v>0.09584533113944879</v>
+      </c>
+      <c r="X4">
+        <v>0.05891032623222175</v>
+      </c>
+      <c r="Y4">
+        <v>0.03693500490722704</v>
+      </c>
+      <c r="Z4">
+        <v>26.01423487544485</v>
+      </c>
+      <c r="AA4">
+        <v>0.7754471811200603</v>
+      </c>
+      <c r="AB4">
+        <v>0.05702976450923607</v>
+      </c>
+      <c r="AC4">
+        <v>0.7184174166108243</v>
+      </c>
+      <c r="AD4">
+        <v>13.8</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>13.8</v>
+      </c>
+      <c r="AG4">
+        <v>-174.3</v>
+      </c>
+      <c r="AH4">
+        <v>0.114713216957606</v>
+      </c>
+      <c r="AI4">
+        <v>0.04574080212131257</v>
+      </c>
+      <c r="AJ4">
+        <v>2.570796460176992</v>
+      </c>
+      <c r="AK4">
+        <v>-1.534330985915493</v>
+      </c>
+      <c r="AL4">
+        <v>0.795</v>
+      </c>
+      <c r="AM4">
+        <v>-5.965</v>
+      </c>
+      <c r="AN4">
+        <v>0.2749003984063745</v>
+      </c>
+      <c r="AO4">
+        <v>35.47169811320754</v>
+      </c>
+      <c r="AP4">
+        <v>-3.47211155378486</v>
+      </c>
+      <c r="AQ4">
+        <v>-4.727577535624476</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>COOCON Corporation (KOSDAQ:A294570)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>0.3879496402877698</v>
+      </c>
+      <c r="H5">
+        <v>0.3003597122302158</v>
+      </c>
+      <c r="I5">
+        <v>0.210431654676259</v>
+      </c>
+      <c r="J5">
+        <v>0.1861764208985062</v>
+      </c>
+      <c r="K5">
+        <v>4.53</v>
+      </c>
+      <c r="L5">
+        <v>0.08147482014388489</v>
+      </c>
+      <c r="M5">
+        <v>3.0052</v>
+      </c>
+      <c r="N5">
+        <v>0.02673665480427046</v>
+      </c>
+      <c r="O5">
+        <v>0.6633995584988962</v>
+      </c>
+      <c r="P5">
+        <v>0.7751999999999999</v>
+      </c>
+      <c r="Q5">
+        <v>0.00689679715302491</v>
+      </c>
+      <c r="R5">
+        <v>0.1711258278145695</v>
+      </c>
+      <c r="S5">
+        <v>2.23</v>
+      </c>
+      <c r="T5">
+        <v>0.7420471183282311</v>
+      </c>
+      <c r="U5">
+        <v>74.2</v>
+      </c>
+      <c r="V5">
+        <v>0.6601423487544484</v>
+      </c>
+      <c r="W5">
+        <v>0.04471865745310958</v>
+      </c>
+      <c r="X5">
+        <v>0.05817324882502302</v>
+      </c>
+      <c r="Y5">
+        <v>-0.01345459137191344</v>
+      </c>
+      <c r="Z5">
+        <v>1.114005209376879</v>
+      </c>
+      <c r="AA5">
+        <v>0.2074015027440783</v>
+      </c>
+      <c r="AB5">
+        <v>0.05758432884692648</v>
+      </c>
+      <c r="AC5">
+        <v>0.1498171738971518</v>
+      </c>
+      <c r="AD5">
+        <v>5.32</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>5.32</v>
+      </c>
+      <c r="AG5">
+        <v>-68.88</v>
+      </c>
+      <c r="AH5">
+        <v>0.04519198097179749</v>
+      </c>
+      <c r="AI5">
+        <v>0.04925013886317348</v>
+      </c>
+      <c r="AJ5">
+        <v>-1.582720588235294</v>
+      </c>
+      <c r="AK5">
+        <v>-2.036664695446481</v>
+      </c>
+      <c r="AL5">
+        <v>0.262</v>
+      </c>
+      <c r="AM5">
+        <v>-0.738</v>
+      </c>
+      <c r="AN5">
+        <v>0.3388535031847134</v>
+      </c>
+      <c r="AO5">
+        <v>44.65648854961832</v>
+      </c>
+      <c r="AP5">
+        <v>-4.387261146496815</v>
+      </c>
+      <c r="AQ5">
+        <v>-15.85365853658537</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Korea Information &amp; Communications Co., Ltd. (KOSDAQ:A025770)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.105</v>
+      </c>
+      <c r="E6">
+        <v>0.131</v>
+      </c>
+      <c r="G6">
+        <v>0.05876559422193039</v>
+      </c>
+      <c r="H6">
+        <v>0.05876559422193039</v>
+      </c>
+      <c r="I6">
+        <v>0.04973736047275115</v>
+      </c>
+      <c r="J6">
+        <v>0.03647406434668417</v>
+      </c>
+      <c r="K6">
+        <v>33</v>
+      </c>
+      <c r="L6">
+        <v>0.05416940249507551</v>
+      </c>
+      <c r="M6">
+        <v>1.99</v>
+      </c>
+      <c r="N6">
+        <v>0.01054583995760466</v>
+      </c>
+      <c r="O6">
+        <v>0.0603030303030303</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>-0</v>
+      </c>
+      <c r="S6">
+        <v>1.99</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>109.3</v>
+      </c>
+      <c r="V6">
+        <v>0.5792262851086381</v>
+      </c>
+      <c r="W6">
+        <v>0.1641791044776119</v>
+      </c>
+      <c r="X6">
+        <v>0.05836172927043601</v>
+      </c>
+      <c r="Y6">
+        <v>0.1058173752071759</v>
+      </c>
+      <c r="Z6">
+        <v>4.215916955017302</v>
+      </c>
+      <c r="AA6">
+        <v>0.1537716262975779</v>
+      </c>
+      <c r="AB6">
+        <v>0.05751580694256883</v>
+      </c>
+      <c r="AC6">
+        <v>0.09625581935500904</v>
+      </c>
+      <c r="AD6">
+        <v>12.9</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>12.9</v>
+      </c>
+      <c r="AG6">
+        <v>-96.39999999999999</v>
+      </c>
+      <c r="AH6">
+        <v>0.06398809523809525</v>
+      </c>
+      <c r="AI6">
+        <v>0.05170340681362726</v>
+      </c>
+      <c r="AJ6">
+        <v>-1.04442036836403</v>
+      </c>
+      <c r="AK6">
+        <v>-0.6875891583452212</v>
+      </c>
+      <c r="AL6">
+        <v>0.349</v>
+      </c>
+      <c r="AM6">
+        <v>-4.061</v>
+      </c>
+      <c r="AN6">
+        <v>0.3274111675126904</v>
+      </c>
+      <c r="AO6">
+        <v>86.81948424068769</v>
+      </c>
+      <c r="AP6">
+        <v>-2.446700507614213</v>
+      </c>
+      <c r="AQ6">
+        <v>-7.461216449150456</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SCI Information Service Inc. (KOSDAQ:A036120)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>-0.0672</v>
+      </c>
+      <c r="E7">
+        <v>-0.161</v>
+      </c>
+      <c r="G7">
+        <v>0.07383512544802869</v>
+      </c>
+      <c r="H7">
+        <v>0.07383512544802869</v>
+      </c>
+      <c r="I7">
+        <v>0.1121863799283154</v>
+      </c>
+      <c r="J7">
+        <v>0.08071060612656539</v>
+      </c>
+      <c r="K7">
+        <v>1.8</v>
+      </c>
+      <c r="L7">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="M7">
+        <v>2.281</v>
+      </c>
+      <c r="N7">
+        <v>0.04044326241134752</v>
+      </c>
+      <c r="O7">
+        <v>1.267222222222222</v>
+      </c>
+      <c r="P7">
+        <v>1.292</v>
+      </c>
+      <c r="Q7">
+        <v>0.02290780141843972</v>
+      </c>
+      <c r="R7">
+        <v>0.7177777777777777</v>
+      </c>
+      <c r="S7">
+        <v>0.9890000000000001</v>
+      </c>
+      <c r="T7">
+        <v>0.4335817623849189</v>
+      </c>
+      <c r="U7">
+        <v>9.49</v>
+      </c>
+      <c r="V7">
+        <v>0.1682624113475177</v>
+      </c>
+      <c r="W7">
+        <v>0.08219178082191782</v>
+      </c>
+      <c r="X7">
+        <v>0.05781851594909689</v>
+      </c>
+      <c r="Y7">
+        <v>0.02437326487282093</v>
+      </c>
+      <c r="Z7">
+        <v>1.428864078664345</v>
+      </c>
+      <c r="AA7">
+        <v>0.1153244858614757</v>
+      </c>
+      <c r="AB7">
+        <v>0.05773546478893734</v>
+      </c>
+      <c r="AC7">
+        <v>0.05758902107253835</v>
+      </c>
+      <c r="AD7">
+        <v>0.437</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0.437</v>
+      </c>
+      <c r="AG7">
+        <v>-9.053000000000001</v>
+      </c>
+      <c r="AH7">
+        <v>0.007688653517954854</v>
+      </c>
+      <c r="AI7">
+        <v>0.01810498404938476</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.1912053561999705</v>
+      </c>
+      <c r="AK7">
+        <v>-0.61807878746501</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0.09238900634249471</v>
+      </c>
+      <c r="AP7">
+        <v>-1.913953488372093</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FnGuide Inc. (KOSDAQ:A064850)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G8">
+        <v>0.2443514644351465</v>
+      </c>
+      <c r="H8">
+        <v>0.2443514644351465</v>
+      </c>
+      <c r="I8">
+        <v>0.2205020920502092</v>
+      </c>
+      <c r="J8">
+        <v>0.2007392489452942</v>
+      </c>
+      <c r="K8">
+        <v>4.4</v>
+      </c>
+      <c r="L8">
+        <v>0.1841004184100419</v>
+      </c>
+      <c r="M8">
+        <v>1.5618</v>
+      </c>
+      <c r="N8">
+        <v>0.02585761589403974</v>
+      </c>
+      <c r="O8">
+        <v>0.3549545454545455</v>
+      </c>
+      <c r="P8">
+        <v>1.5618</v>
+      </c>
+      <c r="Q8">
+        <v>0.02585761589403974</v>
+      </c>
+      <c r="R8">
+        <v>0.3549545454545455</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>7.44</v>
+      </c>
+      <c r="V8">
+        <v>0.1231788079470199</v>
+      </c>
+      <c r="W8">
+        <v>0.1030444964871194</v>
+      </c>
+      <c r="X8">
+        <v>0.0600637170713358</v>
+      </c>
+      <c r="Y8">
+        <v>0.04298077941578364</v>
+      </c>
+      <c r="Z8">
+        <v>0.4781912765106042</v>
+      </c>
+      <c r="AA8">
+        <v>0.09599175769893017</v>
+      </c>
+      <c r="AB8">
+        <v>0.05738565208836741</v>
+      </c>
+      <c r="AC8">
+        <v>0.03860610561056277</v>
+      </c>
+      <c r="AD8">
+        <v>15.6</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>15.6</v>
+      </c>
+      <c r="AG8">
+        <v>8.16</v>
+      </c>
+      <c r="AH8">
+        <v>0.2052631578947368</v>
+      </c>
+      <c r="AI8">
+        <v>0.2492012779552716</v>
+      </c>
+      <c r="AJ8">
+        <v>0.1190198366394399</v>
+      </c>
+      <c r="AK8">
+        <v>0.1479332849891226</v>
+      </c>
+      <c r="AL8">
+        <v>0.613</v>
+      </c>
+      <c r="AM8">
+        <v>0.117</v>
+      </c>
+      <c r="AN8">
+        <v>2.468354430379747</v>
+      </c>
+      <c r="AO8">
+        <v>8.597063621533442</v>
+      </c>
+      <c r="AP8">
+        <v>1.291139240506329</v>
+      </c>
+      <c r="AQ8">
+        <v>45.04273504273504</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kginicis Co.,Ltd (KOSDAQ:A035600)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.129</v>
+      </c>
+      <c r="E9">
+        <v>0.0479</v>
+      </c>
+      <c r="G9">
+        <v>0.1095482546201232</v>
+      </c>
+      <c r="H9">
+        <v>0.1082695538547695</v>
+      </c>
+      <c r="I9">
+        <v>0.05656150830688818</v>
+      </c>
+      <c r="J9">
+        <v>0.04192205909804653</v>
+      </c>
+      <c r="K9">
+        <v>41.4</v>
+      </c>
+      <c r="L9">
+        <v>0.03864103042747806</v>
+      </c>
+      <c r="M9">
+        <v>8.512</v>
+      </c>
+      <c r="N9">
+        <v>0.05343377275580665</v>
+      </c>
+      <c r="O9">
+        <v>0.2056038647342995</v>
+      </c>
+      <c r="P9">
+        <v>8.512</v>
+      </c>
+      <c r="Q9">
+        <v>0.05343377275580665</v>
+      </c>
+      <c r="R9">
+        <v>0.2056038647342995</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>75.5</v>
+      </c>
+      <c r="V9">
+        <v>0.4739485247959824</v>
+      </c>
+      <c r="W9">
+        <v>0.1221959858323495</v>
+      </c>
+      <c r="X9">
+        <v>0.07419874993193584</v>
+      </c>
+      <c r="Y9">
+        <v>0.04799723590041362</v>
+      </c>
+      <c r="Z9">
+        <v>2.09135272301386</v>
+      </c>
+      <c r="AA9">
+        <v>0.08767381244904757</v>
+      </c>
+      <c r="AB9">
+        <v>0.05368995756787921</v>
+      </c>
+      <c r="AC9">
+        <v>0.03398385488116836</v>
+      </c>
+      <c r="AD9">
+        <v>292.4</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>292.4</v>
+      </c>
+      <c r="AG9">
+        <v>216.9</v>
+      </c>
+      <c r="AH9">
+        <v>0.6473323001992473</v>
+      </c>
+      <c r="AI9">
+        <v>0.3584211816621721</v>
+      </c>
+      <c r="AJ9">
+        <v>0.5765550239234449</v>
+      </c>
+      <c r="AK9">
+        <v>0.2929893286505471</v>
+      </c>
+      <c r="AL9">
+        <v>12.9</v>
+      </c>
+      <c r="AM9">
+        <v>7.86</v>
+      </c>
+      <c r="AN9">
+        <v>3.11063829787234</v>
+      </c>
+      <c r="AO9">
+        <v>4.697674418604652</v>
+      </c>
+      <c r="AP9">
+        <v>2.307446808510638</v>
+      </c>
+      <c r="AQ9">
+        <v>7.709923664122138</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NICE Holdings Co., Ltd. (KOSE:A034310)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.121</v>
+      </c>
+      <c r="G10">
+        <v>0.1053448658239077</v>
+      </c>
+      <c r="H10">
+        <v>0.09638500776225328</v>
+      </c>
+      <c r="I10">
+        <v>0.05340430250609891</v>
+      </c>
+      <c r="J10">
+        <v>0.02670215125304946</v>
+      </c>
+      <c r="K10">
+        <v>-1.68</v>
+      </c>
+      <c r="L10">
+        <v>-0.0007451763140385895</v>
+      </c>
+      <c r="M10">
+        <v>31.705</v>
+      </c>
+      <c r="N10">
+        <v>0.123126213592233</v>
+      </c>
+      <c r="O10">
+        <v>-18.87202380952381</v>
+      </c>
+      <c r="P10">
+        <v>12.005</v>
+      </c>
+      <c r="Q10">
+        <v>0.04662135922330098</v>
+      </c>
+      <c r="R10">
+        <v>-7.145833333333334</v>
+      </c>
+      <c r="S10">
+        <v>19.7</v>
+      </c>
+      <c r="T10">
+        <v>0.6213530988803027</v>
+      </c>
+      <c r="U10">
+        <v>409.4</v>
+      </c>
+      <c r="V10">
+        <v>1.589902912621359</v>
+      </c>
+      <c r="W10">
+        <v>-0.00282780676653762</v>
+      </c>
+      <c r="X10">
+        <v>0.08308924354330741</v>
+      </c>
+      <c r="Y10">
+        <v>-0.08591705030984502</v>
+      </c>
+      <c r="Z10">
+        <v>2.917313664596273</v>
+      </c>
+      <c r="AA10">
+        <v>0.07789855072463768</v>
+      </c>
+      <c r="AB10">
+        <v>0.05644111618045349</v>
+      </c>
+      <c r="AC10">
+        <v>0.02145743454418419</v>
+      </c>
+      <c r="AD10">
+        <v>728.1</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>728.1</v>
+      </c>
+      <c r="AG10">
+        <v>318.7</v>
+      </c>
+      <c r="AH10">
+        <v>0.7387378246753247</v>
+      </c>
+      <c r="AI10">
+        <v>0.4194366034909845</v>
+      </c>
+      <c r="AJ10">
+        <v>0.5531065602221451</v>
+      </c>
+      <c r="AK10">
+        <v>0.2402563136072371</v>
+      </c>
+      <c r="AL10">
+        <v>45.5</v>
+      </c>
+      <c r="AM10">
+        <v>24.9</v>
+      </c>
+      <c r="AN10">
+        <v>2.752741020793951</v>
+      </c>
+      <c r="AO10">
+        <v>2.646153846153846</v>
+      </c>
+      <c r="AP10">
+        <v>1.204914933837429</v>
+      </c>
+      <c r="AQ10">
+        <v>4.835341365461848</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Galaxia Moneytree Co., Ltd. (KOSDAQ:A094480)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.09029999999999999</v>
+      </c>
+      <c r="E11">
+        <v>-0.127</v>
+      </c>
+      <c r="G11">
+        <v>0.07874015748031496</v>
+      </c>
+      <c r="H11">
+        <v>0.07874015748031496</v>
+      </c>
+      <c r="I11">
+        <v>0.08740157480314961</v>
+      </c>
+      <c r="J11">
+        <v>0.04710427551696224</v>
+      </c>
+      <c r="K11">
+        <v>1.78</v>
+      </c>
+      <c r="L11">
+        <v>0.01751968503937008</v>
+      </c>
+      <c r="M11">
+        <v>1.3328</v>
+      </c>
+      <c r="N11">
+        <v>0.006584980237154151</v>
+      </c>
+      <c r="O11">
+        <v>0.7487640449438203</v>
+      </c>
+      <c r="P11">
+        <v>1.3328</v>
+      </c>
+      <c r="Q11">
+        <v>0.006584980237154151</v>
+      </c>
+      <c r="R11">
+        <v>0.7487640449438203</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>4.66</v>
+      </c>
+      <c r="V11">
+        <v>0.02302371541501976</v>
+      </c>
+      <c r="W11">
+        <v>0.02077012835472579</v>
+      </c>
+      <c r="X11">
+        <v>0.06150382757498846</v>
+      </c>
+      <c r="Y11">
+        <v>-0.04073369922026267</v>
+      </c>
+      <c r="Z11">
+        <v>0.8873362445414846</v>
+      </c>
+      <c r="AA11">
+        <v>0.04179733093906868</v>
+      </c>
+      <c r="AB11">
+        <v>0.05862142663369257</v>
+      </c>
+      <c r="AC11">
+        <v>-0.01682409569462389</v>
+      </c>
+      <c r="AD11">
+        <v>84.8</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>84.8</v>
+      </c>
+      <c r="AG11">
+        <v>80.14</v>
+      </c>
+      <c r="AH11">
+        <v>0.2952646239554317</v>
+      </c>
+      <c r="AI11">
+        <v>0.4904569115095431</v>
+      </c>
+      <c r="AJ11">
+        <v>0.2836412543356693</v>
+      </c>
+      <c r="AK11">
+        <v>0.4763433190679981</v>
+      </c>
+      <c r="AL11">
+        <v>4.42</v>
+      </c>
+      <c r="AM11">
+        <v>4.295</v>
+      </c>
+      <c r="AN11">
+        <v>8.153846153846153</v>
+      </c>
+      <c r="AO11">
+        <v>2.009049773755657</v>
+      </c>
+      <c r="AP11">
+        <v>7.70576923076923</v>
+      </c>
+      <c r="AQ11">
+        <v>2.067520372526193</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The LEADCORP, Inc. (KOSDAQ:A012700)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>-0.027</v>
+      </c>
+      <c r="E12">
+        <v>-0.292</v>
+      </c>
+      <c r="G12">
+        <v>0.06154699196007762</v>
+      </c>
+      <c r="H12">
+        <v>0.06154699196007762</v>
+      </c>
+      <c r="I12">
+        <v>0.07152758525090103</v>
+      </c>
+      <c r="J12">
+        <v>0.03576379262545051</v>
+      </c>
+      <c r="K12">
+        <v>5.28</v>
+      </c>
+      <c r="L12">
+        <v>0.01463820349320765</v>
+      </c>
+      <c r="M12">
+        <v>3.8912</v>
+      </c>
+      <c r="N12">
+        <v>0.05582783357245337</v>
+      </c>
+      <c r="O12">
+        <v>0.7369696969696969</v>
+      </c>
+      <c r="P12">
+        <v>3.8912</v>
+      </c>
+      <c r="Q12">
+        <v>0.05582783357245337</v>
+      </c>
+      <c r="R12">
+        <v>0.7369696969696969</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>38.3</v>
+      </c>
+      <c r="V12">
+        <v>0.5494978479196556</v>
+      </c>
+      <c r="W12">
+        <v>0.01704875686147885</v>
+      </c>
+      <c r="X12">
+        <v>0.06642801706126161</v>
+      </c>
+      <c r="Y12">
+        <v>-0.04937926019978276</v>
+      </c>
+      <c r="Z12">
+        <v>1.019214467363662</v>
+      </c>
+      <c r="AA12">
+        <v>0.03645097485165302</v>
+      </c>
+      <c r="AB12">
+        <v>0.05466408398021777</v>
+      </c>
+      <c r="AC12">
+        <v>-0.01821310912856475</v>
+      </c>
+      <c r="AD12">
+        <v>67.5</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>67.5</v>
+      </c>
+      <c r="AG12">
+        <v>29.2</v>
+      </c>
+      <c r="AH12">
+        <v>0.4919825072886298</v>
+      </c>
+      <c r="AI12">
+        <v>0.1755526657997399</v>
+      </c>
+      <c r="AJ12">
+        <v>0.295247724974722</v>
+      </c>
+      <c r="AK12">
+        <v>0.08434430964760255</v>
+      </c>
+      <c r="AL12">
+        <v>28.3</v>
+      </c>
+      <c r="AM12">
+        <v>27.629</v>
+      </c>
+      <c r="AN12">
+        <v>2.402135231316726</v>
+      </c>
+      <c r="AO12">
+        <v>0.911660777385159</v>
+      </c>
+      <c r="AP12">
+        <v>1.03914590747331</v>
+      </c>
+      <c r="AQ12">
+        <v>0.9338014405154005</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KG Mobilians Co., Ltd (KOSDAQ:A046440)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.08460000000000001</v>
+      </c>
+      <c r="E13">
+        <v>0.206</v>
+      </c>
+      <c r="G13">
+        <v>0.1518609967992684</v>
+      </c>
+      <c r="H13">
+        <v>0.1486053955189758</v>
+      </c>
+      <c r="I13">
+        <v>0.03662551440329218</v>
+      </c>
+      <c r="J13">
+        <v>0.02683127572016461</v>
+      </c>
+      <c r="K13">
+        <v>20.8</v>
+      </c>
+      <c r="L13">
+        <v>0.0951074531321445</v>
+      </c>
+      <c r="M13">
+        <v>6.232800000000001</v>
+      </c>
+      <c r="N13">
+        <v>0.05228859060402685</v>
+      </c>
+      <c r="O13">
+        <v>0.2996538461538462</v>
+      </c>
+      <c r="P13">
+        <v>6.232800000000001</v>
+      </c>
+      <c r="Q13">
+        <v>0.05228859060402685</v>
+      </c>
+      <c r="R13">
+        <v>0.2996538461538462</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>24.8</v>
+      </c>
+      <c r="V13">
+        <v>0.2080536912751678</v>
+      </c>
+      <c r="W13">
+        <v>0.08768971332209106</v>
+      </c>
+      <c r="X13">
+        <v>0.06096690834536574</v>
+      </c>
+      <c r="Y13">
+        <v>0.02672280497672533</v>
+      </c>
+      <c r="Z13">
+        <v>0.7907010376369356</v>
+      </c>
+      <c r="AA13">
+        <v>0.02121551755305687</v>
+      </c>
+      <c r="AB13">
+        <v>0.05678593631052721</v>
+      </c>
+      <c r="AC13">
+        <v>-0.03557041875747034</v>
+      </c>
+      <c r="AD13">
+        <v>42.8</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>42.8</v>
+      </c>
+      <c r="AG13">
+        <v>18</v>
+      </c>
+      <c r="AH13">
+        <v>0.2641975308641975</v>
+      </c>
+      <c r="AI13">
+        <v>0.1401440733464309</v>
+      </c>
+      <c r="AJ13">
+        <v>0.1311953352769679</v>
+      </c>
+      <c r="AK13">
+        <v>0.06414825374198145</v>
+      </c>
+      <c r="AL13">
+        <v>2.3</v>
+      </c>
+      <c r="AM13">
+        <v>0.6999999999999997</v>
+      </c>
+      <c r="AN13">
+        <v>2.891891891891892</v>
+      </c>
+      <c r="AO13">
+        <v>3.482608695652174</v>
+      </c>
+      <c r="AP13">
+        <v>1.216216216216216</v>
+      </c>
+      <c r="AQ13">
+        <v>11.44285714285715</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Danal Co., Ltd. (KOSDAQ:A064260)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.0793</v>
+      </c>
+      <c r="G14">
+        <v>0.06784182944259172</v>
+      </c>
+      <c r="H14">
+        <v>0.04587898999523583</v>
+      </c>
+      <c r="I14">
+        <v>0.01991424487851358</v>
+      </c>
+      <c r="J14">
+        <v>0.01991424487851358</v>
+      </c>
+      <c r="K14">
+        <v>-18.2</v>
+      </c>
+      <c r="L14">
+        <v>-0.08670795616960457</v>
+      </c>
+      <c r="M14">
+        <v>-0</v>
+      </c>
+      <c r="N14">
+        <v>-0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>-0</v>
+      </c>
+      <c r="Q14">
+        <v>-0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>42.6</v>
+      </c>
+      <c r="V14">
+        <v>0.3312597200622084</v>
+      </c>
+      <c r="W14">
+        <v>-0.07801114444920702</v>
+      </c>
+      <c r="X14">
+        <v>0.07308728950199225</v>
+      </c>
+      <c r="Y14">
+        <v>-0.1510984339511993</v>
+      </c>
+      <c r="Z14">
+        <v>0.5374196686893514</v>
+      </c>
+      <c r="AA14">
+        <v>0.01070230688480938</v>
+      </c>
+      <c r="AB14">
+        <v>0.0554480098765507</v>
+      </c>
+      <c r="AC14">
+        <v>-0.04474570299174132</v>
+      </c>
+      <c r="AD14">
+        <v>220.1</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>220.1</v>
+      </c>
+      <c r="AG14">
+        <v>177.5</v>
+      </c>
+      <c r="AH14">
+        <v>0.631201605965013</v>
+      </c>
+      <c r="AI14">
+        <v>0.4985277463193658</v>
+      </c>
+      <c r="AJ14">
+        <v>0.579875857562888</v>
+      </c>
+      <c r="AK14">
+        <v>0.444973677613437</v>
+      </c>
+      <c r="AL14">
+        <v>10</v>
+      </c>
+      <c r="AM14">
+        <v>7.82</v>
+      </c>
+      <c r="AN14">
+        <v>21.16346153846154</v>
+      </c>
+      <c r="AO14">
+        <v>0.418</v>
+      </c>
+      <c r="AP14">
+        <v>17.06730769230769</v>
+      </c>
+      <c r="AQ14">
+        <v>0.5345268542199488</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Han Kook Capital.Co., Ltd (KOSDAQ:A023760)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0.158</v>
+      </c>
+      <c r="E15">
+        <v>0.298</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>57.8</v>
+      </c>
+      <c r="L15">
+        <v>0.4718367346938775</v>
+      </c>
+      <c r="M15">
+        <v>6.5667</v>
+      </c>
+      <c r="N15">
+        <v>0.05670725388601036</v>
+      </c>
+      <c r="O15">
+        <v>0.1136107266435986</v>
+      </c>
+      <c r="P15">
+        <v>6.5667</v>
+      </c>
+      <c r="Q15">
+        <v>0.05670725388601036</v>
+      </c>
+      <c r="R15">
+        <v>0.1136107266435986</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>71.8</v>
+      </c>
+      <c r="V15">
+        <v>0.6200345423143351</v>
+      </c>
+      <c r="W15">
+        <v>0.1557951482479784</v>
+      </c>
+      <c r="X15">
+        <v>0.2505208262160893</v>
+      </c>
+      <c r="Y15">
+        <v>-0.09472567796811085</v>
+      </c>
+      <c r="Z15">
+        <v>0.05105868622874292</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0.05175710436586283</v>
+      </c>
+      <c r="AC15">
+        <v>-0.05175710436586283</v>
+      </c>
+      <c r="AD15">
+        <v>2490.9</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>2490.9</v>
+      </c>
+      <c r="AG15">
+        <v>2419.1</v>
+      </c>
+      <c r="AH15">
+        <v>0.9555760156519737</v>
+      </c>
+      <c r="AI15">
+        <v>0.8327983951855567</v>
+      </c>
+      <c r="AJ15">
+        <v>0.9543177245650716</v>
+      </c>
+      <c r="AK15">
+        <v>0.8286859413537956</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Samsung Card Co., Ltd. (KOSE:A029780)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="E16">
+        <v>0.15</v>
+      </c>
+      <c r="K16">
+        <v>541.2</v>
+      </c>
+      <c r="M16">
+        <v>202.73</v>
+      </c>
+      <c r="N16">
+        <v>0.07113333333333333</v>
+      </c>
+      <c r="O16">
+        <v>0.3745934959349593</v>
+      </c>
+      <c r="P16">
+        <v>202.73</v>
+      </c>
+      <c r="Q16">
+        <v>0.07113333333333333</v>
+      </c>
+      <c r="R16">
+        <v>0.3745934959349593</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>653.5</v>
+      </c>
+      <c r="V16">
+        <v>0.2292982456140351</v>
+      </c>
+      <c r="W16">
+        <v>0.09072317028195931</v>
+      </c>
+      <c r="X16">
+        <v>0.09935765350355975</v>
+      </c>
+      <c r="Y16">
+        <v>-0.008634483221600445</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0.05258977240371818</v>
+      </c>
+      <c r="AC16">
+        <v>-0.05258977240371818</v>
+      </c>
+      <c r="AD16">
+        <v>13232.2</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>13232.2</v>
+      </c>
+      <c r="AG16">
+        <v>12578.7</v>
+      </c>
+      <c r="AH16">
+        <v>0.822785439803012</v>
+      </c>
+      <c r="AI16">
+        <v>0.6749676089817488</v>
+      </c>
+      <c r="AJ16">
+        <v>0.8152793171168018</v>
+      </c>
+      <c r="AK16">
+        <v>0.6637591223543193</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Meritz Financial Group Inc. (KOSE:A138040)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>0.0329</v>
+      </c>
+      <c r="E17">
+        <v>0.463</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>1772.3</v>
+      </c>
+      <c r="L17">
+        <v>0.1650585802894556</v>
+      </c>
+      <c r="M17">
+        <v>891.1799999999999</v>
+      </c>
+      <c r="N17">
+        <v>0.06949747332959011</v>
+      </c>
+      <c r="O17">
+        <v>0.5028381199571178</v>
+      </c>
+      <c r="P17">
+        <v>327.78</v>
+      </c>
+      <c r="Q17">
+        <v>0.02556148231330713</v>
+      </c>
+      <c r="R17">
+        <v>0.1849461152175139</v>
+      </c>
+      <c r="S17">
+        <v>563.4</v>
+      </c>
+      <c r="T17">
+        <v>0.6321955160573621</v>
+      </c>
+      <c r="U17">
+        <v>3764.5</v>
+      </c>
+      <c r="V17">
+        <v>0.2935694678395408</v>
+      </c>
+      <c r="W17">
+        <v>0.2536531608249488</v>
+      </c>
+      <c r="X17">
+        <v>0.09001772406742412</v>
+      </c>
+      <c r="Y17">
+        <v>0.1636354367575247</v>
+      </c>
+      <c r="Z17">
+        <v>0.2661632962663665</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0.05489593199080755</v>
+      </c>
+      <c r="AC17">
+        <v>-0.05489593199080755</v>
+      </c>
+      <c r="AD17">
+        <v>46172.3</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>46172.3</v>
+      </c>
+      <c r="AG17">
+        <v>42407.8</v>
+      </c>
+      <c r="AH17">
+        <v>0.7826410488935597</v>
+      </c>
+      <c r="AI17">
+        <v>0.8497176950370272</v>
+      </c>
+      <c r="AJ17">
+        <v>0.767826039724068</v>
+      </c>
+      <c r="AK17">
+        <v>0.8385313373103518</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>Mirae Asset Securities Co., Ltd. (KOSE:A006800)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D18">
         <v>0.0278</v>
       </c>
-      <c r="E3">
+      <c r="E18">
         <v>-0.00557</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
         <v>407.3</v>
       </c>
-      <c r="L3">
+      <c r="L18">
         <v>0.03775456289800799</v>
       </c>
-      <c r="M3">
+      <c r="M18">
         <v>222.9</v>
       </c>
-      <c r="N3">
+      <c r="N18">
         <v>0.08043737144094404</v>
       </c>
-      <c r="O3">
+      <c r="O18">
         <v>0.5472624601031181</v>
       </c>
-      <c r="P3">
+      <c r="P18">
         <v>68.40000000000001</v>
       </c>
-      <c r="Q3">
+      <c r="Q18">
         <v>0.02468333874634622</v>
       </c>
-      <c r="R3">
+      <c r="R18">
         <v>0.1679351829118586</v>
       </c>
-      <c r="S3">
+      <c r="S18">
         <v>154.5</v>
       </c>
-      <c r="T3">
+      <c r="T18">
         <v>0.693135935397039</v>
       </c>
-      <c r="U3">
+      <c r="U18">
         <v>1421.3</v>
       </c>
-      <c r="V3">
+      <c r="V18">
         <v>0.5129010140377468</v>
       </c>
-      <c r="W3">
+      <c r="W18">
         <v>0.04836200857288735</v>
       </c>
-      <c r="X3">
-        <v>0.2728832009162179</v>
-      </c>
-      <c r="Y3">
-        <v>-0.2245211923433306</v>
-      </c>
-      <c r="Z3">
+      <c r="X18">
+        <v>0.2727710321689567</v>
+      </c>
+      <c r="Y18">
+        <v>-0.2244090235960693</v>
+      </c>
+      <c r="Z18">
         <v>0.1658365691763281</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.05605387102388523</v>
-      </c>
-      <c r="AC3">
-        <v>-0.05605387102388523</v>
-      </c>
-      <c r="AD3">
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0.05604938304312422</v>
+      </c>
+      <c r="AC18">
+        <v>-0.05604938304312422</v>
+      </c>
+      <c r="AD18">
         <v>66487.39999999999</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
         <v>66487.39999999999</v>
       </c>
-      <c r="AG3">
+      <c r="AG18">
         <v>65066.09999999999</v>
       </c>
-      <c r="AH3">
+      <c r="AH18">
         <v>0.9599890266176714</v>
       </c>
-      <c r="AI3">
+      <c r="AI18">
         <v>0.8840092964877571</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ18">
         <v>0.9591507314570765</v>
       </c>
-      <c r="AK3">
+      <c r="AK18">
         <v>0.8817751480893726</v>
       </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Mason Capital Corporation (KOSDAQ:A021880)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>0.157</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>-4.34</v>
+      </c>
+      <c r="L19">
+        <v>-0.3528455284552845</v>
+      </c>
+      <c r="M19">
+        <v>-0</v>
+      </c>
+      <c r="N19">
+        <v>-0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>-0</v>
+      </c>
+      <c r="Q19">
+        <v>-0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>5.94</v>
+      </c>
+      <c r="V19">
+        <v>0.2076923076923077</v>
+      </c>
+      <c r="W19">
+        <v>-0.1014018691588785</v>
+      </c>
+      <c r="X19">
+        <v>0.05989552493309078</v>
+      </c>
+      <c r="Y19">
+        <v>-0.1612973940919693</v>
+      </c>
+      <c r="Z19">
+        <v>0.2817869415807561</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0.05704465133314778</v>
+      </c>
+      <c r="AC19">
+        <v>-0.05704465133314778</v>
+      </c>
+      <c r="AD19">
+        <v>6.85</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>6.85</v>
+      </c>
+      <c r="AG19">
+        <v>0.9099999999999993</v>
+      </c>
+      <c r="AH19">
+        <v>0.1932299012693935</v>
+      </c>
+      <c r="AI19">
+        <v>0.1431556948798328</v>
+      </c>
+      <c r="AJ19">
+        <v>0.03083700440528632</v>
+      </c>
+      <c r="AK19">
+        <v>0.02171319494154138</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Yuanta 11 Special Purpose Acquisition Company (KOSDAQ:A444920)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="K20">
+        <v>0.195</v>
+      </c>
+      <c r="M20">
+        <v>-0</v>
+      </c>
+      <c r="N20">
+        <v>-0</v>
+      </c>
+      <c r="O20">
+        <v>-0</v>
+      </c>
+      <c r="P20">
+        <v>-0</v>
+      </c>
+      <c r="Q20">
+        <v>-0</v>
+      </c>
+      <c r="R20">
+        <v>-0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0.299</v>
+      </c>
+      <c r="V20">
+        <v>0.04229137199434229</v>
+      </c>
+      <c r="W20">
+        <v>0.02535760728218465</v>
+      </c>
+      <c r="X20">
+        <v>0.05920679771410058</v>
+      </c>
+      <c r="Y20">
+        <v>-0.03384919043191592</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0.05750137514997744</v>
+      </c>
+      <c r="AC20">
+        <v>-0.05750137514997744</v>
+      </c>
+      <c r="AD20">
+        <v>1.15</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>1.15</v>
+      </c>
+      <c r="AG20">
+        <v>0.851</v>
+      </c>
+      <c r="AH20">
+        <v>0.1399026763990267</v>
+      </c>
+      <c r="AI20">
+        <v>0.1245937161430119</v>
+      </c>
+      <c r="AJ20">
+        <v>0.1074359298068426</v>
+      </c>
+      <c r="AK20">
+        <v>0.09528608218564549</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-0.319</v>
+      </c>
+      <c r="AQ20">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Yuanta 10 SPECIAL PURPOSE ACQUISITION COMPANY (KOSDAQ:A435380)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="K21">
+        <v>0.251</v>
+      </c>
+      <c r="M21">
+        <v>-0</v>
+      </c>
+      <c r="N21">
+        <v>-0</v>
+      </c>
+      <c r="O21">
+        <v>-0</v>
+      </c>
+      <c r="P21">
+        <v>-0</v>
+      </c>
+      <c r="Q21">
+        <v>-0</v>
+      </c>
+      <c r="R21">
+        <v>-0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0.207</v>
+      </c>
+      <c r="V21">
+        <v>0.02571428571428571</v>
+      </c>
+      <c r="W21">
+        <v>0.02915214866434379</v>
+      </c>
+      <c r="X21">
+        <v>0.05906273420586673</v>
+      </c>
+      <c r="Y21">
+        <v>-0.02991058554152294</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0.05752272548927194</v>
+      </c>
+      <c r="AC21">
+        <v>-0.05752272548927194</v>
+      </c>
+      <c r="AD21">
+        <v>1.18</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>1.18</v>
+      </c>
+      <c r="AG21">
+        <v>0.973</v>
+      </c>
+      <c r="AH21">
+        <v>0.1278439869989166</v>
+      </c>
+      <c r="AI21">
+        <v>0.1151219512195122</v>
+      </c>
+      <c r="AJ21">
+        <v>0.1078355314197052</v>
+      </c>
+      <c r="AK21">
+        <v>0.09688340137409139</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>-0.384</v>
+      </c>
+      <c r="AQ21">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kakao Pay Corp. (KOSE:A377300)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="F22">
+        <v>1.963</v>
+      </c>
+      <c r="G22">
+        <v>-0.01419639573372563</v>
+      </c>
+      <c r="H22">
+        <v>-0.01419639573372563</v>
+      </c>
+      <c r="I22">
+        <v>-0.06436189775652815</v>
+      </c>
+      <c r="J22">
+        <v>-0.06436189775652815</v>
+      </c>
+      <c r="K22">
+        <v>-15</v>
+      </c>
+      <c r="L22">
+        <v>-0.02758367046708349</v>
+      </c>
+      <c r="M22">
+        <v>-0</v>
+      </c>
+      <c r="N22">
+        <v>-0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>-0</v>
+      </c>
+      <c r="Q22">
+        <v>-0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>1213.9</v>
+      </c>
+      <c r="V22">
+        <v>0.5073984283564621</v>
+      </c>
+      <c r="W22">
+        <v>-0.01074575542660649</v>
+      </c>
+      <c r="X22">
+        <v>0.05801204344320053</v>
+      </c>
+      <c r="Y22">
+        <v>-0.06875779886980701</v>
+      </c>
+      <c r="Z22">
+        <v>0.8638602065131056</v>
+      </c>
+      <c r="AA22">
+        <v>-0.05559968228752978</v>
+      </c>
+      <c r="AB22">
+        <v>0.0576451565206471</v>
+      </c>
+      <c r="AC22">
+        <v>-0.1132448388081769</v>
+      </c>
+      <c r="AD22">
+        <v>70.2</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>70.2</v>
+      </c>
+      <c r="AG22">
+        <v>-1143.7</v>
+      </c>
+      <c r="AH22">
+        <v>0.02850645659059531</v>
+      </c>
+      <c r="AI22">
+        <v>0.04609323703217334</v>
+      </c>
+      <c r="AJ22">
+        <v>-0.915912549051013</v>
+      </c>
+      <c r="AK22">
+        <v>-3.700097055968943</v>
+      </c>
+      <c r="AL22">
+        <v>4.51</v>
+      </c>
+      <c r="AM22">
+        <v>-43.29</v>
+      </c>
+      <c r="AN22">
+        <v>21.01796407185629</v>
+      </c>
+      <c r="AO22">
+        <v>-7.760532150776053</v>
+      </c>
+      <c r="AP22">
+        <v>-342.4251497005988</v>
+      </c>
+      <c r="AQ22">
+        <v>0.8085008085008085</v>
       </c>
     </row>
   </sheetData>
